--- a/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_40.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3249092.639821582</v>
+        <v>3249649.32018881</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40452611.1726255</v>
+        <v>40452611.17262551</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>2.241794397568981</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -708,16 +708,16 @@
         <v>60.31193664654398</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>180.0411395175086</v>
       </c>
       <c r="U2" t="n">
-        <v>12.73575832880961</v>
+        <v>72.93641320887008</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606677</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>238</v>
       </c>
-      <c r="G3" t="n">
-        <v>236.7166455835123</v>
-      </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>58.22174631810037</v>
       </c>
       <c r="I3" t="n">
-        <v>189.207046268707</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.28560429088162</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>96.92651427351137</v>
       </c>
       <c r="S3" t="n">
-        <v>51.50178298347925</v>
+        <v>238</v>
       </c>
       <c r="T3" t="n">
         <v>2.089246349589303</v>
@@ -793,7 +793,7 @@
         <v>0.1570107035829551</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>238</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -857,13 +857,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>12.54083132625466</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -945,10 +945,10 @@
         <v>60.31193664654398</v>
       </c>
       <c r="T5" t="n">
-        <v>180.0411395175086</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>82.60000634813885</v>
+        <v>213.1665676226534</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>85.58039172754714</v>
+        <v>238</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>69.56786886406448</v>
       </c>
       <c r="R6" t="n">
-        <v>238</v>
+        <v>96.92651427351137</v>
       </c>
       <c r="S6" t="n">
-        <v>238</v>
+        <v>51.50178298347925</v>
       </c>
       <c r="T6" t="n">
         <v>2.089246349589303</v>
@@ -1030,10 +1030,10 @@
         <v>0.1570107035829551</v>
       </c>
       <c r="V6" t="n">
+        <v>207.5252373803851</v>
+      </c>
+      <c r="W6" t="n">
         <v>238</v>
-      </c>
-      <c r="W6" t="n">
-        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1049,49 +1049,49 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>12.54083132625466</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76.97469500161772</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1143,7 +1143,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.241794397568981</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1179,25 +1179,25 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>60.31193664654398</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>180.0411395175086</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>229.8510241668239</v>
+      </c>
+      <c r="W8" t="n">
         <v>238</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>114.5530723285093</v>
       </c>
     </row>
     <row r="9">
@@ -1210,16 +1210,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>238</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>238</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>69.56786886406448</v>
       </c>
       <c r="R9" t="n">
-        <v>96.92651427351137</v>
+        <v>238</v>
       </c>
       <c r="S9" t="n">
-        <v>51.50178298347925</v>
+        <v>238</v>
       </c>
       <c r="T9" t="n">
         <v>2.089246349589303</v>
@@ -1267,7 +1267,7 @@
         <v>0.1570107035829551</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>85.58039172754714</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>160.6414272790364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1316,13 +1316,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>12.54083132625466</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>12.54083132625466</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1368,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>219.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>180.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1419,19 +1419,19 @@
         <v>230.311936646544</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="V11" t="n">
-        <v>55.50472937061232</v>
+        <v>217.318463353456</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>154.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>131.0999124455193</v>
@@ -1507,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>73.15664575996374</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>189.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>108.4628285590246</v>
       </c>
     </row>
     <row r="13">
@@ -1556,25 +1556,25 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>108.8147895088055</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>237.1516162552914</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>228.4921969423622</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>120.5257911782653</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1608,19 +1608,19 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>180.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>174.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>172.241794397569</v>
       </c>
       <c r="H14" t="n">
-        <v>162.4882466432259</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>167.9133689089124</v>
+        <v>230.311936646544</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>45.07666895588699</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>109.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>94.92863021464998</v>
@@ -1729,16 +1729,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>106.0445343735739</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>221.5017829834792</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>170.157010703583</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>184.5106671915202</v>
@@ -1747,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>189.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>35.27835012154546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1766,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>55.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>50.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>44.38285596774193</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.8935067594019289</v>
       </c>
       <c r="M16" t="n">
-        <v>20.97524897735455</v>
+        <v>184.064217959927</v>
       </c>
       <c r="N16" t="n">
         <v>237.1516162552914</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>57.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1842,19 +1842,19 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>219.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>180.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>174.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>113.5748716195872</v>
+        <v>174.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>172.241794397569</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1896,13 +1896,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>156.0383259452697</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>238</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>131.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>117.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>109.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>94.92863021464998</v>
       </c>
       <c r="H18" t="n">
         <v>94.33644567698717</v>
@@ -1966,16 +1966,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>172.6175146673914</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>221.5017829834792</v>
       </c>
       <c r="T18" t="n">
-        <v>59.14665662451168</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>170.157010703583</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1984,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>189.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>169.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2000,13 +2000,13 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>42.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>50.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>92.47454619056604</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>184.064217959927</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>228.4921969423622</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>38.78192845740566</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>57.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="C20" t="n">
-        <v>219.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>180.3391557398498</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>174.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>172.241794397569</v>
+        <v>104.8029976169242</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>162.4882466432259</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2130,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>238</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>119.0243986514252</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>154.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>131.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>117.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>112.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>168.9615452191472</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>170.157010703583</v>
+        <v>94.20913150511201</v>
       </c>
       <c r="V21" t="n">
         <v>184.5106671915202</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>169.3913927661343</v>
@@ -2234,16 +2234,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>42.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>50.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>92.47454619056604</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>184.064217959927</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>77.67224512028238</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>120.5257911782653</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2300,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>11.96228876414156</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>57.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -2313,25 +2313,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>219.4745782429939</v>
       </c>
       <c r="D23" t="n">
         <v>180.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>167.9133689089123</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>174.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>162.4882466432259</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>230.311936646544</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>55.50472937061232</v>
       </c>
     </row>
     <row r="24">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>154.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2401,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>112.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>109.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>94.92863021464998</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>94.33644567698717</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.598367944592199</v>
+        <v>238</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>46.7635369825221</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>170.157010703583</v>
       </c>
       <c r="V24" t="n">
         <v>184.5106671915202</v>
@@ -2458,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>169.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>42.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>55.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>14.36403677595626</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2507,19 +2507,19 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>237.1516162552914</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>229.3405806870708</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>58.40134261334349</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>57.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>162.0671999999998</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2583,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>99.01373617365952</v>
+        <v>99.01373617365931</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="T26" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>162.0671999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2632,22 +2632,22 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>147.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>128.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>110.92863021465</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>110.3364456769872</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>162.0671999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>33.03011444093073</v>
+        <v>184</v>
       </c>
       <c r="T27" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>73.11380033707866</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>20.27077102939265</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>8.726765445880911</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>108.474546190566</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>79.47495330995818</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>12.37280983870968</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>73.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2793,19 +2793,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>184.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>162.0671999999998</v>
+        <v>167.578953356774</v>
       </c>
       <c r="F29" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>178.4882466432259</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>64.13991156191531</v>
       </c>
       <c r="N29" t="n">
-        <v>34.87382461174425</v>
+        <v>34.87382461174403</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>184.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>170.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>104.5560976508707</v>
       </c>
       <c r="D30" t="n">
         <v>133.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>128.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>125.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>110.92863021465</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>4.307880564333513</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>71.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>8.726765445880911</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>108.474546190566</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>119.3757153941989</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>132.0917165939583</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3033,10 +3033,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>168.578953356775</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>63.13991156191531</v>
+        <v>99.01373617365931</v>
       </c>
       <c r="N32" t="n">
-        <v>35.87382461174315</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>168.578953356774</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>103.2008828876481</v>
+        <v>169.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>146.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>132.9376868977026</v>
@@ -3115,13 +3115,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>124.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>109.92863021465</v>
+        <v>31.50035599558727</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>109.3364456769872</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3169,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>184.0000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3182,16 +3182,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>72.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>70.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>65.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>7.726765445880911</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3212,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>107.474546190566</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>174.7504242159336</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3227,13 +3227,13 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.27032125863282</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>135.5257911782653</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>11.37280983870968</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>184.0000000000031</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>184.0000000000033</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>162.0671999999908</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>63.13991156191531</v>
+        <v>99.01373617365931</v>
       </c>
       <c r="N35" t="n">
-        <v>35.87382461174406</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>162.0671999999999</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>184.0000000000027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3343,22 +3343,22 @@
         <v>169.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>146.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>127.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>124.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>105.0742852311667</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>109.3364456769872</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3397,19 +3397,19 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>184</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>108.2023037938838</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>72.11380033707866</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>70.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>7.726765445880911</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>123.3137814449688</v>
+        <v>54.16241505712019</v>
       </c>
       <c r="S37" t="n">
-        <v>135.5257911782653</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>11.37280983870968</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>162.0671999999999</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>177.4882466432259</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,16 +3549,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>184</v>
       </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>168.578953356774</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>162.0671999999998</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3631,10 +3631,10 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>184.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="V39" t="n">
         <v>184</v>
@@ -3646,7 +3646,7 @@
         <v>184</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>162.0671999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>72.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>18.80166920363289</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>7.726765445880911</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3686,26 +3686,26 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>73.26199034171088</v>
+        <v>107.474546190566</v>
       </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>184</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>11.37280983870968</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>71.41535690022275</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>184.000000000002</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3783,19 +3783,19 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>154.6756792303045</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>100.7396776699254</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>184.0000000000026</v>
+        <v>184</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>184.0000000000025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3829,13 +3829,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>184.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>184.0000000000003</v>
+        <v>184</v>
       </c>
       <c r="I42" t="n">
-        <v>93.49933113593482</v>
+        <v>184</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>93.49933113593546</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>13.52093132625466</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>13.52093132625466</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>100.7396776699255</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>184.000000000002</v>
+        <v>184</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="H44" t="n">
-        <v>100.739677669923</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>90.65184309977002</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>99.01373617365931</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>184.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4069,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>184.0000000000003</v>
+        <v>184</v>
       </c>
       <c r="I45" t="n">
-        <v>93.49933113593289</v>
+        <v>184</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>68.56786886406448</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>184.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4117,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="Y45" t="n">
-        <v>184.0000000000019</v>
+        <v>162.0671999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4133,40 +4133,40 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
         <v>13.52093132625466</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91.0687340356497</v>
+        <v>88.80429525022647</v>
       </c>
       <c r="C2" t="n">
-        <v>41.09441257808007</v>
+        <v>38.82997379265686</v>
       </c>
       <c r="D2" t="n">
-        <v>30.65082092166615</v>
+        <v>28.38638213624293</v>
       </c>
       <c r="E2" t="n">
-        <v>26.24345768240488</v>
+        <v>23.97901889698167</v>
       </c>
       <c r="F2" t="n">
-        <v>21.30443878542321</v>
+        <v>19.04</v>
       </c>
       <c r="G2" t="n">
         <v>19.04</v>
@@ -4330,7 +4330,7 @@
         <v>538.1731939681143</v>
       </c>
       <c r="M2" t="n">
-        <v>538.1731939681144</v>
+        <v>553.2627594141035</v>
       </c>
       <c r="N2" t="n">
         <v>553.2627594141035</v>
@@ -4351,22 +4351,22 @@
         <v>733.8306910334863</v>
       </c>
       <c r="T2" t="n">
-        <v>733.8306910334863</v>
+        <v>551.9709541471141</v>
       </c>
       <c r="U2" t="n">
-        <v>720.9662886811534</v>
+        <v>478.2978094916897</v>
       </c>
       <c r="V2" t="n">
-        <v>720.9662886811534</v>
+        <v>478.2978094916897</v>
       </c>
       <c r="W2" t="n">
-        <v>480.562248277113</v>
+        <v>478.2978094916897</v>
       </c>
       <c r="X2" t="n">
-        <v>286.3381740744183</v>
+        <v>284.0737352889951</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.8963228796644</v>
+        <v>171.6318840942411</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>689.6699917699185</v>
+        <v>318.2538851697984</v>
       </c>
       <c r="C3" t="n">
-        <v>689.6699917699185</v>
+        <v>318.2538851697984</v>
       </c>
       <c r="D3" t="n">
-        <v>689.6699917699185</v>
+        <v>318.2538851697984</v>
       </c>
       <c r="E3" t="n">
-        <v>689.6699917699185</v>
+        <v>318.2538851697984</v>
       </c>
       <c r="F3" t="n">
-        <v>449.2659513658781</v>
+        <v>318.2538851697984</v>
       </c>
       <c r="G3" t="n">
-        <v>210.1582285542495</v>
+        <v>77.84984476575795</v>
       </c>
       <c r="H3" t="n">
-        <v>210.1582285542495</v>
+        <v>19.04</v>
       </c>
       <c r="I3" t="n">
         <v>19.04</v>
@@ -4403,16 +4403,16 @@
         <v>218.8431940432235</v>
       </c>
       <c r="K3" t="n">
-        <v>244.7486180039782</v>
+        <v>454.4631940432235</v>
       </c>
       <c r="L3" t="n">
-        <v>480.3686180039782</v>
+        <v>690.0831940432236</v>
       </c>
       <c r="M3" t="n">
-        <v>715.9886180039782</v>
+        <v>690.0831940432236</v>
       </c>
       <c r="N3" t="n">
-        <v>851.937714381813</v>
+        <v>690.0831940432236</v>
       </c>
       <c r="O3" t="n">
         <v>903.130919309241</v>
@@ -4421,31 +4421,31 @@
         <v>952</v>
       </c>
       <c r="Q3" t="n">
-        <v>909.2872683930489</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>811.381698419805</v>
+        <v>854.0944300267562</v>
       </c>
       <c r="S3" t="n">
-        <v>759.3596954061896</v>
+        <v>613.6903896227158</v>
       </c>
       <c r="T3" t="n">
-        <v>757.2493455581197</v>
+        <v>611.5800397746458</v>
       </c>
       <c r="U3" t="n">
-        <v>757.0907488878339</v>
+        <v>611.42144310436</v>
       </c>
       <c r="V3" t="n">
-        <v>742.4335093004398</v>
+        <v>371.0174027003196</v>
       </c>
       <c r="W3" t="n">
-        <v>709.7333649470777</v>
+        <v>338.3172583469575</v>
       </c>
       <c r="X3" t="n">
-        <v>689.6699917699185</v>
+        <v>318.2538851697984</v>
       </c>
       <c r="Y3" t="n">
-        <v>689.6699917699185</v>
+        <v>318.2538851697984</v>
       </c>
     </row>
     <row r="4">
@@ -4500,10 +4500,10 @@
         <v>31.70750639015622</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.04</v>
+        <v>31.70750639015622</v>
       </c>
       <c r="R4" t="n">
-        <v>19.04</v>
+        <v>31.70750639015622</v>
       </c>
       <c r="S4" t="n">
         <v>19.04</v>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.09441257808007</v>
+        <v>91.0687340356497</v>
       </c>
       <c r="C5" t="n">
         <v>41.09441257808007</v>
@@ -4567,7 +4567,7 @@
         <v>538.1731939681143</v>
       </c>
       <c r="M5" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="N5" t="n">
         <v>553.2627594141035</v>
@@ -4588,22 +4588,22 @@
         <v>733.8306910334863</v>
       </c>
       <c r="T5" t="n">
-        <v>551.9709541471141</v>
+        <v>733.8306910334863</v>
       </c>
       <c r="U5" t="n">
-        <v>468.5366043005092</v>
+        <v>518.5109257580789</v>
       </c>
       <c r="V5" t="n">
-        <v>236.3638526168486</v>
+        <v>286.3381740744183</v>
       </c>
       <c r="W5" t="n">
-        <v>236.3638526168486</v>
+        <v>286.3381740744183</v>
       </c>
       <c r="X5" t="n">
-        <v>236.3638526168486</v>
+        <v>286.3381740744183</v>
       </c>
       <c r="Y5" t="n">
-        <v>123.9220014220947</v>
+        <v>173.8963228796644</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="C6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="D6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="E6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="F6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="G6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="H6" t="n">
         <v>19.04</v>
@@ -4643,13 +4643,13 @@
         <v>244.7486180039782</v>
       </c>
       <c r="L6" t="n">
-        <v>431.890919309241</v>
+        <v>380.6977143818129</v>
       </c>
       <c r="M6" t="n">
-        <v>667.510919309241</v>
+        <v>616.3177143818129</v>
       </c>
       <c r="N6" t="n">
-        <v>667.510919309241</v>
+        <v>851.937714381813</v>
       </c>
       <c r="O6" t="n">
         <v>903.130919309241</v>
@@ -4661,28 +4661,28 @@
         <v>881.7294253898339</v>
       </c>
       <c r="R6" t="n">
-        <v>641.3253849857934</v>
+        <v>783.82385541659</v>
       </c>
       <c r="S6" t="n">
-        <v>400.921344581753</v>
+        <v>731.8018524029746</v>
       </c>
       <c r="T6" t="n">
-        <v>398.810994733683</v>
+        <v>729.6915025549047</v>
       </c>
       <c r="U6" t="n">
-        <v>398.6523980633972</v>
+        <v>729.5329058846189</v>
       </c>
       <c r="V6" t="n">
-        <v>158.2483576593568</v>
+        <v>519.91145398524</v>
       </c>
       <c r="W6" t="n">
-        <v>125.5482133059946</v>
+        <v>279.5074135811996</v>
       </c>
       <c r="X6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="Y6" t="n">
-        <v>105.4848401288355</v>
+        <v>259.4440404040404</v>
       </c>
     </row>
     <row r="7">
@@ -4734,34 +4734,34 @@
         <v>31.70750639015622</v>
       </c>
       <c r="P7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="R7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="S7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="T7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="U7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="V7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="W7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="X7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="8">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.39693201096522</v>
+        <v>86.66137079638843</v>
       </c>
       <c r="C8" t="n">
-        <v>34.4226105533956</v>
+        <v>36.68704933881881</v>
       </c>
       <c r="D8" t="n">
-        <v>23.97901889698167</v>
+        <v>26.24345768240488</v>
       </c>
       <c r="E8" t="n">
-        <v>23.97901889698167</v>
+        <v>26.24345768240488</v>
       </c>
       <c r="F8" t="n">
-        <v>19.04</v>
+        <v>21.30443878542321</v>
       </c>
       <c r="G8" t="n">
         <v>19.04</v>
@@ -4798,10 +4798,10 @@
         <v>111.6938749228882</v>
       </c>
       <c r="K8" t="n">
-        <v>317.6427594141035</v>
+        <v>302.5531939681143</v>
       </c>
       <c r="L8" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="M8" t="n">
         <v>553.2627594141035</v>
@@ -4822,25 +4822,25 @@
         <v>952</v>
       </c>
       <c r="S8" t="n">
-        <v>891.0788518721778</v>
+        <v>952</v>
       </c>
       <c r="T8" t="n">
-        <v>709.2191149858055</v>
+        <v>952</v>
       </c>
       <c r="U8" t="n">
-        <v>468.8150745817651</v>
+        <v>952</v>
       </c>
       <c r="V8" t="n">
-        <v>468.8150745817651</v>
+        <v>719.8272483163395</v>
       </c>
       <c r="W8" t="n">
-        <v>468.8150745817651</v>
+        <v>479.4232079122991</v>
       </c>
       <c r="X8" t="n">
-        <v>274.5910003790704</v>
+        <v>285.1991337096044</v>
       </c>
       <c r="Y8" t="n">
-        <v>162.1491491843165</v>
+        <v>169.4889596404031</v>
       </c>
     </row>
     <row r="9">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>499.8480808080809</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="C9" t="n">
         <v>259.4440404040404</v>
@@ -4859,7 +4859,7 @@
         <v>259.4440404040404</v>
       </c>
       <c r="E9" t="n">
-        <v>19.04</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="F9" t="n">
         <v>19.04</v>
@@ -4874,22 +4874,22 @@
         <v>19.04</v>
       </c>
       <c r="J9" t="n">
-        <v>19.04</v>
+        <v>218.8431940432235</v>
       </c>
       <c r="K9" t="n">
-        <v>254.66</v>
+        <v>244.7486180039782</v>
       </c>
       <c r="L9" t="n">
-        <v>316.1109916132075</v>
+        <v>306.1996096171858</v>
       </c>
       <c r="M9" t="n">
-        <v>551.7309916132076</v>
+        <v>541.8196096171857</v>
       </c>
       <c r="N9" t="n">
-        <v>665.186795072572</v>
+        <v>777.4396096171857</v>
       </c>
       <c r="O9" t="n">
-        <v>716.38</v>
+        <v>903.130919309241</v>
       </c>
       <c r="P9" t="n">
         <v>952</v>
@@ -4898,28 +4898,28 @@
         <v>881.7294253898339</v>
       </c>
       <c r="R9" t="n">
-        <v>783.82385541659</v>
+        <v>641.3253849857934</v>
       </c>
       <c r="S9" t="n">
-        <v>731.8018524029746</v>
+        <v>400.921344581753</v>
       </c>
       <c r="T9" t="n">
-        <v>729.6915025549047</v>
+        <v>398.810994733683</v>
       </c>
       <c r="U9" t="n">
-        <v>729.5329058846189</v>
+        <v>398.6523980633972</v>
       </c>
       <c r="V9" t="n">
-        <v>714.8756662972248</v>
+        <v>312.2075579345617</v>
       </c>
       <c r="W9" t="n">
-        <v>682.1755219438627</v>
+        <v>279.5074135811996</v>
       </c>
       <c r="X9" t="n">
-        <v>662.1121487667035</v>
+        <v>259.4440404040404</v>
       </c>
       <c r="Y9" t="n">
-        <v>499.8480808080809</v>
+        <v>259.4440404040404</v>
       </c>
     </row>
     <row r="10">
@@ -4959,10 +4959,10 @@
         <v>31.70750639015622</v>
       </c>
       <c r="L10" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="M10" t="n">
-        <v>31.70750639015622</v>
+        <v>19.04</v>
       </c>
       <c r="N10" t="n">
         <v>19.04</v>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>422.892256548327</v>
+        <v>19.04</v>
       </c>
       <c r="C11" t="n">
-        <v>201.2007633735857</v>
+        <v>19.04</v>
       </c>
       <c r="D11" t="n">
         <v>19.04</v>
@@ -5029,31 +5029,31 @@
         <v>19.04</v>
       </c>
       <c r="I11" t="n">
-        <v>34.12956544598914</v>
+        <v>19.04</v>
       </c>
       <c r="J11" t="n">
-        <v>126.7834403688774</v>
+        <v>111.6938749228882</v>
       </c>
       <c r="K11" t="n">
-        <v>317.6427594141035</v>
+        <v>302.5531939681143</v>
       </c>
       <c r="L11" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="M11" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="N11" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="O11" t="n">
-        <v>736.521614415149</v>
+        <v>721.4320489691598</v>
       </c>
       <c r="P11" t="n">
-        <v>952</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="Q11" t="n">
-        <v>952</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="R11" t="n">
         <v>952</v>
@@ -5062,22 +5062,22 @@
         <v>719.3616801550061</v>
       </c>
       <c r="T11" t="n">
-        <v>719.3616801550061</v>
+        <v>478.9576397509657</v>
       </c>
       <c r="U11" t="n">
-        <v>719.3616801550061</v>
+        <v>238.5535993469252</v>
       </c>
       <c r="V11" t="n">
-        <v>663.2962969523674</v>
+        <v>19.04</v>
       </c>
       <c r="W11" t="n">
-        <v>663.2962969523674</v>
+        <v>19.04</v>
       </c>
       <c r="X11" t="n">
-        <v>422.892256548327</v>
+        <v>19.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>422.892256548327</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="12">
@@ -5108,25 +5108,25 @@
         <v>19.04</v>
       </c>
       <c r="I12" t="n">
-        <v>59.42502419398005</v>
+        <v>19.04</v>
       </c>
       <c r="J12" t="n">
-        <v>261.738123728693</v>
+        <v>221.353099534713</v>
       </c>
       <c r="K12" t="n">
-        <v>287.6435476894478</v>
+        <v>247.2585234954677</v>
       </c>
       <c r="L12" t="n">
-        <v>349.0945393026553</v>
+        <v>308.7095151086752</v>
       </c>
       <c r="M12" t="n">
-        <v>399.3075588197082</v>
+        <v>308.7095151086752</v>
       </c>
       <c r="N12" t="n">
-        <v>634.9275588197082</v>
+        <v>397.92937451472</v>
       </c>
       <c r="O12" t="n">
-        <v>761.4055528747629</v>
+        <v>574.6546335655219</v>
       </c>
       <c r="P12" t="n">
         <v>810.2746335655219</v>
@@ -5150,13 +5150,13 @@
         <v>952</v>
       </c>
       <c r="W12" t="n">
-        <v>878.1043982222589</v>
+        <v>952</v>
       </c>
       <c r="X12" t="n">
-        <v>686.323853327928</v>
+        <v>952</v>
       </c>
       <c r="Y12" t="n">
-        <v>686.323853327928</v>
+        <v>842.4415873141165</v>
       </c>
     </row>
     <row r="13">
@@ -5199,22 +5199,22 @@
         <v>490.2442393357194</v>
       </c>
       <c r="M13" t="n">
-        <v>380.3303105389462</v>
+        <v>490.2442393357194</v>
       </c>
       <c r="N13" t="n">
-        <v>140.7832234123892</v>
+        <v>490.2442393357194</v>
       </c>
       <c r="O13" t="n">
-        <v>140.7832234123892</v>
+        <v>490.2442393357194</v>
       </c>
       <c r="P13" t="n">
-        <v>140.7832234123892</v>
+        <v>249.840198931679</v>
       </c>
       <c r="Q13" t="n">
-        <v>140.7832234123892</v>
+        <v>19.04</v>
       </c>
       <c r="R13" t="n">
-        <v>140.7832234123892</v>
+        <v>19.04</v>
       </c>
       <c r="S13" t="n">
         <v>19.04</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>541.9864960516036</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="C14" t="n">
-        <v>541.9864960516036</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="D14" t="n">
-        <v>359.825732678018</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="E14" t="n">
-        <v>359.825732678018</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="F14" t="n">
-        <v>183.1695420638646</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="G14" t="n">
-        <v>183.1695420638646</v>
+        <v>19.04</v>
       </c>
       <c r="H14" t="n">
         <v>19.04</v>
@@ -5269,52 +5269,52 @@
         <v>19.04</v>
       </c>
       <c r="J14" t="n">
-        <v>126.7834403688774</v>
+        <v>111.6938749228882</v>
       </c>
       <c r="K14" t="n">
-        <v>317.6427594141035</v>
+        <v>302.5531939681143</v>
       </c>
       <c r="L14" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="M14" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="N14" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="O14" t="n">
-        <v>736.521614415149</v>
+        <v>721.4320489691598</v>
       </c>
       <c r="P14" t="n">
-        <v>952</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="Q14" t="n">
-        <v>952</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="R14" t="n">
         <v>952</v>
       </c>
       <c r="S14" t="n">
-        <v>782.390536455644</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="T14" t="n">
-        <v>782.390536455644</v>
+        <v>478.9576397509657</v>
       </c>
       <c r="U14" t="n">
-        <v>782.390536455644</v>
+        <v>238.5535993469252</v>
       </c>
       <c r="V14" t="n">
-        <v>782.390536455644</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="W14" t="n">
-        <v>782.390536455644</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="X14" t="n">
-        <v>782.390536455644</v>
+        <v>193.0216105025949</v>
       </c>
       <c r="Y14" t="n">
-        <v>541.9864960516036</v>
+        <v>193.0216105025949</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>210.2168443349871</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="C15" t="n">
-        <v>210.2168443349871</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="D15" t="n">
-        <v>210.2168443349871</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="E15" t="n">
-        <v>210.2168443349871</v>
+        <v>320.9605234641556</v>
       </c>
       <c r="F15" t="n">
         <v>210.2168443349871</v>
@@ -5345,55 +5345,55 @@
         <v>19.04</v>
       </c>
       <c r="I15" t="n">
-        <v>41.87471812037627</v>
+        <v>19.04</v>
       </c>
       <c r="J15" t="n">
-        <v>244.1878176550892</v>
+        <v>221.353099534713</v>
       </c>
       <c r="K15" t="n">
-        <v>479.8078176550893</v>
+        <v>247.2585234954677</v>
       </c>
       <c r="L15" t="n">
-        <v>603.890045151192</v>
+        <v>308.7095151086752</v>
       </c>
       <c r="M15" t="n">
-        <v>603.890045151192</v>
+        <v>544.3295151086752</v>
       </c>
       <c r="N15" t="n">
-        <v>693.1099045572367</v>
+        <v>544.3295151086752</v>
       </c>
       <c r="O15" t="n">
-        <v>744.3031094846648</v>
+        <v>595.5227200361032</v>
       </c>
       <c r="P15" t="n">
-        <v>793.1721901754238</v>
+        <v>810.2746335655219</v>
       </c>
       <c r="Q15" t="n">
         <v>952</v>
       </c>
       <c r="R15" t="n">
-        <v>952</v>
+        <v>844.8843087135617</v>
       </c>
       <c r="S15" t="n">
-        <v>952</v>
+        <v>621.1451339827746</v>
       </c>
       <c r="T15" t="n">
-        <v>952</v>
+        <v>621.1451339827746</v>
       </c>
       <c r="U15" t="n">
-        <v>780.1242316125424</v>
+        <v>621.1451339827746</v>
       </c>
       <c r="V15" t="n">
-        <v>593.7498203079766</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="W15" t="n">
-        <v>593.7498203079766</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="X15" t="n">
-        <v>401.9692754136457</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="Y15" t="n">
-        <v>366.3345783211756</v>
+        <v>434.7707226782088</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>171.4642210709636</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="C16" t="n">
-        <v>171.4642210709636</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="D16" t="n">
-        <v>115.367031115857</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="E16" t="n">
-        <v>63.87116764418377</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="F16" t="n">
+        <v>109.2604330034491</v>
+      </c>
+      <c r="G16" t="n">
+        <v>109.2604330034491</v>
+      </c>
+      <c r="H16" t="n">
+        <v>116.460935212027</v>
+      </c>
+      <c r="I16" t="n">
+        <v>189.5338934923722</v>
+      </c>
+      <c r="J16" t="n">
+        <v>425.1538934923722</v>
+      </c>
+      <c r="K16" t="n">
+        <v>445.4130716915357</v>
+      </c>
+      <c r="L16" t="n">
+        <v>444.5105396113317</v>
+      </c>
+      <c r="M16" t="n">
+        <v>258.587087126557</v>
+      </c>
+      <c r="N16" t="n">
         <v>19.04</v>
       </c>
-      <c r="G16" t="n">
+      <c r="O16" t="n">
         <v>19.04</v>
       </c>
-      <c r="H16" t="n">
-        <v>26.2405022085779</v>
-      </c>
-      <c r="I16" t="n">
-        <v>99.3134604889231</v>
-      </c>
-      <c r="J16" t="n">
-        <v>334.9334604889231</v>
-      </c>
-      <c r="K16" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="L16" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="M16" t="n">
-        <v>334.0055185089406</v>
-      </c>
-      <c r="N16" t="n">
-        <v>94.45843138238357</v>
-      </c>
-      <c r="O16" t="n">
-        <v>94.45843138238357</v>
-      </c>
       <c r="P16" t="n">
-        <v>94.45843138238357</v>
+        <v>19.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.45843138238357</v>
+        <v>19.04</v>
       </c>
       <c r="R16" t="n">
-        <v>94.45843138238357</v>
+        <v>19.04</v>
       </c>
       <c r="S16" t="n">
-        <v>94.45843138238357</v>
+        <v>19.04</v>
       </c>
       <c r="T16" t="n">
-        <v>117.1098170985655</v>
+        <v>41.69138571618191</v>
       </c>
       <c r="U16" t="n">
-        <v>195.3977208843931</v>
+        <v>119.9792895020095</v>
       </c>
       <c r="V16" t="n">
-        <v>225.9191137703391</v>
+        <v>150.5006823879555</v>
       </c>
       <c r="W16" t="n">
-        <v>229.5100320300165</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="X16" t="n">
-        <v>229.5100320300165</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="Y16" t="n">
-        <v>171.4642210709636</v>
+        <v>154.0916006476329</v>
       </c>
     </row>
     <row r="17">
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>711.5959595959596</v>
+        <v>553.981488944172</v>
       </c>
       <c r="C17" t="n">
-        <v>489.9044664212182</v>
+        <v>553.981488944172</v>
       </c>
       <c r="D17" t="n">
-        <v>307.7437030476326</v>
+        <v>371.8207255705864</v>
       </c>
       <c r="E17" t="n">
-        <v>307.7437030476326</v>
+        <v>195.6961906141534</v>
       </c>
       <c r="F17" t="n">
-        <v>193.0216105025949</v>
+        <v>19.04</v>
       </c>
       <c r="G17" t="n">
         <v>19.04</v>
@@ -5509,25 +5509,25 @@
         <v>111.6938749228882</v>
       </c>
       <c r="K17" t="n">
-        <v>317.6427594141035</v>
+        <v>302.5531939681143</v>
       </c>
       <c r="L17" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="M17" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="N17" t="n">
-        <v>553.2627594141035</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="O17" t="n">
-        <v>736.521614415149</v>
+        <v>721.4320489691598</v>
       </c>
       <c r="P17" t="n">
-        <v>952</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="Q17" t="n">
-        <v>952</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="R17" t="n">
         <v>952</v>
@@ -5539,19 +5539,19 @@
         <v>952</v>
       </c>
       <c r="U17" t="n">
-        <v>952</v>
+        <v>794.3855293482125</v>
       </c>
       <c r="V17" t="n">
-        <v>711.5959595959596</v>
+        <v>794.3855293482125</v>
       </c>
       <c r="W17" t="n">
-        <v>711.5959595959596</v>
+        <v>553.981488944172</v>
       </c>
       <c r="X17" t="n">
-        <v>711.5959595959596</v>
+        <v>553.981488944172</v>
       </c>
       <c r="Y17" t="n">
-        <v>711.5959595959596</v>
+        <v>553.981488944172</v>
       </c>
     </row>
     <row r="18">
@@ -5561,19 +5561,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>357.4971721822054</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="C18" t="n">
-        <v>225.0730181968324</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="D18" t="n">
-        <v>225.0730181968324</v>
+        <v>434.7707226782088</v>
       </c>
       <c r="E18" t="n">
-        <v>225.0730181968324</v>
+        <v>320.9605234641556</v>
       </c>
       <c r="F18" t="n">
-        <v>114.3293390676638</v>
+        <v>210.2168443349871</v>
       </c>
       <c r="G18" t="n">
         <v>114.3293390676638</v>
@@ -5594,43 +5594,43 @@
         <v>331.5442332290515</v>
       </c>
       <c r="M18" t="n">
-        <v>406.4854650391571</v>
+        <v>509.6825700604272</v>
       </c>
       <c r="N18" t="n">
-        <v>406.4854650391571</v>
+        <v>598.902429466472</v>
       </c>
       <c r="O18" t="n">
-        <v>557.5521901754238</v>
+        <v>761.4055528747629</v>
       </c>
       <c r="P18" t="n">
-        <v>793.1721901754238</v>
+        <v>810.2746335655219</v>
       </c>
       <c r="Q18" t="n">
         <v>952</v>
       </c>
       <c r="R18" t="n">
-        <v>952</v>
+        <v>777.638874073342</v>
       </c>
       <c r="S18" t="n">
-        <v>952</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="T18" t="n">
-        <v>892.2559023994831</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="U18" t="n">
-        <v>720.3801340120256</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="V18" t="n">
-        <v>720.3801340120256</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="W18" t="n">
-        <v>720.3801340120256</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="X18" t="n">
-        <v>528.5995891176947</v>
+        <v>553.8996993425549</v>
       </c>
       <c r="Y18" t="n">
-        <v>357.4971721822054</v>
+        <v>553.8996993425549</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>113.692678267678</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="C19" t="n">
-        <v>70.53586347167328</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="D19" t="n">
-        <v>70.53586347167328</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="E19" t="n">
+        <v>154.0916006476329</v>
+      </c>
+      <c r="F19" t="n">
+        <v>154.0916006476329</v>
+      </c>
+      <c r="G19" t="n">
+        <v>154.0916006476329</v>
+      </c>
+      <c r="H19" t="n">
+        <v>161.2921028562108</v>
+      </c>
+      <c r="I19" t="n">
+        <v>234.365061136556</v>
+      </c>
+      <c r="J19" t="n">
+        <v>469.985061136556</v>
+      </c>
+      <c r="K19" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="L19" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="M19" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="N19" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="O19" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="P19" t="n">
+        <v>259.4440404040404</v>
+      </c>
+      <c r="Q19" t="n">
         <v>19.04</v>
       </c>
-      <c r="F19" t="n">
+      <c r="R19" t="n">
         <v>19.04</v>
       </c>
-      <c r="G19" t="n">
+      <c r="S19" t="n">
         <v>19.04</v>
       </c>
-      <c r="H19" t="n">
-        <v>26.2405022085779</v>
-      </c>
-      <c r="I19" t="n">
-        <v>99.3134604889231</v>
-      </c>
-      <c r="J19" t="n">
-        <v>334.9334604889231</v>
-      </c>
-      <c r="K19" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="L19" t="n">
-        <v>261.7840061723633</v>
-      </c>
-      <c r="M19" t="n">
-        <v>75.86055368758855</v>
-      </c>
-      <c r="N19" t="n">
-        <v>75.86055368758855</v>
-      </c>
-      <c r="O19" t="n">
-        <v>75.86055368758855</v>
-      </c>
-      <c r="P19" t="n">
-        <v>75.86055368758855</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>75.86055368758855</v>
-      </c>
-      <c r="R19" t="n">
-        <v>75.86055368758855</v>
-      </c>
-      <c r="S19" t="n">
-        <v>36.68688857909799</v>
-      </c>
       <c r="T19" t="n">
-        <v>59.3382742952799</v>
+        <v>41.69138571618191</v>
       </c>
       <c r="U19" t="n">
-        <v>137.6261780811075</v>
+        <v>119.9792895020095</v>
       </c>
       <c r="V19" t="n">
-        <v>168.1475709670535</v>
+        <v>150.5006823879555</v>
       </c>
       <c r="W19" t="n">
-        <v>171.7384892267309</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="X19" t="n">
-        <v>171.7384892267309</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="Y19" t="n">
-        <v>113.692678267678</v>
+        <v>154.0916006476329</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>591.3692942914897</v>
+        <v>471.1919191919192</v>
       </c>
       <c r="C20" t="n">
-        <v>369.6778011167484</v>
+        <v>471.1919191919192</v>
       </c>
       <c r="D20" t="n">
-        <v>369.6778011167484</v>
+        <v>289.0311558183335</v>
       </c>
       <c r="E20" t="n">
-        <v>369.6778011167484</v>
+        <v>289.0311558183335</v>
       </c>
       <c r="F20" t="n">
-        <v>193.0216105025949</v>
+        <v>289.0311558183335</v>
       </c>
       <c r="G20" t="n">
-        <v>19.04</v>
+        <v>183.1695420638646</v>
       </c>
       <c r="H20" t="n">
         <v>19.04</v>
@@ -5752,10 +5752,10 @@
         <v>538.1731939681143</v>
       </c>
       <c r="M20" t="n">
-        <v>538.1731939681144</v>
+        <v>553.2627594141035</v>
       </c>
       <c r="N20" t="n">
-        <v>538.1731939681144</v>
+        <v>553.2627594141035</v>
       </c>
       <c r="O20" t="n">
         <v>736.521614415149</v>
@@ -5773,22 +5773,22 @@
         <v>952</v>
       </c>
       <c r="T20" t="n">
+        <v>952</v>
+      </c>
+      <c r="U20" t="n">
+        <v>952</v>
+      </c>
+      <c r="V20" t="n">
+        <v>952</v>
+      </c>
+      <c r="W20" t="n">
+        <v>952</v>
+      </c>
+      <c r="X20" t="n">
+        <v>952</v>
+      </c>
+      <c r="Y20" t="n">
         <v>711.5959595959596</v>
-      </c>
-      <c r="U20" t="n">
-        <v>711.5959595959596</v>
-      </c>
-      <c r="V20" t="n">
-        <v>591.3692942914897</v>
-      </c>
-      <c r="W20" t="n">
-        <v>591.3692942914897</v>
-      </c>
-      <c r="X20" t="n">
-        <v>591.3692942914897</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>591.3692942914897</v>
       </c>
     </row>
     <row r="21">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>251.9791758783992</v>
+        <v>151.464153985373</v>
       </c>
       <c r="C21" t="n">
-        <v>251.9791758783992</v>
+        <v>19.04</v>
       </c>
       <c r="D21" t="n">
-        <v>132.8501992140532</v>
+        <v>19.04</v>
       </c>
       <c r="E21" t="n">
         <v>19.04</v>
@@ -5819,25 +5819,25 @@
         <v>19.04</v>
       </c>
       <c r="I21" t="n">
-        <v>41.87471812037627</v>
+        <v>19.04</v>
       </c>
       <c r="J21" t="n">
-        <v>244.1878176550892</v>
+        <v>19.04</v>
       </c>
       <c r="K21" t="n">
-        <v>270.093241615844</v>
+        <v>228.7145612615553</v>
       </c>
       <c r="L21" t="n">
-        <v>473.2484091210409</v>
+        <v>290.1655528747629</v>
       </c>
       <c r="M21" t="n">
-        <v>523.4614286380938</v>
+        <v>525.7855528747629</v>
       </c>
       <c r="N21" t="n">
-        <v>523.4614286380938</v>
+        <v>525.7855528747629</v>
       </c>
       <c r="O21" t="n">
-        <v>574.6546335655219</v>
+        <v>761.4055528747629</v>
       </c>
       <c r="P21" t="n">
         <v>810.2746335655219</v>
@@ -5852,22 +5852,22 @@
         <v>952</v>
       </c>
       <c r="T21" t="n">
-        <v>781.3317725059119</v>
+        <v>952</v>
       </c>
       <c r="U21" t="n">
-        <v>609.4560041184543</v>
+        <v>856.8392611059475</v>
       </c>
       <c r="V21" t="n">
-        <v>423.0815928138885</v>
+        <v>670.4648498013817</v>
       </c>
       <c r="W21" t="n">
-        <v>423.0815928138885</v>
+        <v>670.4648498013817</v>
       </c>
       <c r="X21" t="n">
-        <v>423.0815928138885</v>
+        <v>478.6843049070508</v>
       </c>
       <c r="Y21" t="n">
-        <v>251.9791758783992</v>
+        <v>307.5818879715615</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>113.692678267678</v>
+        <v>83.96266972480065</v>
       </c>
       <c r="C22" t="n">
-        <v>70.53586347167328</v>
+        <v>83.96266972480065</v>
       </c>
       <c r="D22" t="n">
-        <v>70.53586347167328</v>
+        <v>83.96266972480065</v>
       </c>
       <c r="E22" t="n">
+        <v>83.96266972480065</v>
+      </c>
+      <c r="F22" t="n">
+        <v>83.96266972480065</v>
+      </c>
+      <c r="G22" t="n">
+        <v>83.96266972480065</v>
+      </c>
+      <c r="H22" t="n">
+        <v>91.16317193337855</v>
+      </c>
+      <c r="I22" t="n">
+        <v>164.2361302137238</v>
+      </c>
+      <c r="J22" t="n">
+        <v>399.8561302137238</v>
+      </c>
+      <c r="K22" t="n">
+        <v>420.1153084128872</v>
+      </c>
+      <c r="L22" t="n">
+        <v>326.7066758971639</v>
+      </c>
+      <c r="M22" t="n">
+        <v>140.7832234123892</v>
+      </c>
+      <c r="N22" t="n">
+        <v>140.7832234123892</v>
+      </c>
+      <c r="O22" t="n">
+        <v>140.7832234123892</v>
+      </c>
+      <c r="P22" t="n">
+        <v>140.7832234123892</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>140.7832234123892</v>
+      </c>
+      <c r="R22" t="n">
+        <v>140.7832234123892</v>
+      </c>
+      <c r="S22" t="n">
         <v>19.04</v>
       </c>
-      <c r="F22" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="G22" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="H22" t="n">
-        <v>26.2405022085779</v>
-      </c>
-      <c r="I22" t="n">
-        <v>99.3134604889231</v>
-      </c>
-      <c r="J22" t="n">
-        <v>334.9334604889231</v>
-      </c>
-      <c r="K22" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="L22" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="M22" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="N22" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="O22" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="P22" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>114.7885982840461</v>
-      </c>
-      <c r="R22" t="n">
-        <v>36.33178503123565</v>
-      </c>
-      <c r="S22" t="n">
-        <v>36.33178503123565</v>
-      </c>
       <c r="T22" t="n">
-        <v>58.98317074741756</v>
+        <v>41.69138571618191</v>
       </c>
       <c r="U22" t="n">
-        <v>137.2710745332452</v>
+        <v>119.9792895020095</v>
       </c>
       <c r="V22" t="n">
-        <v>167.7924674191912</v>
+        <v>150.5006823879555</v>
       </c>
       <c r="W22" t="n">
-        <v>171.3833856788686</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="X22" t="n">
-        <v>171.3833856788686</v>
+        <v>142.0084806838535</v>
       </c>
       <c r="Y22" t="n">
-        <v>171.3833856788686</v>
+        <v>83.96266972480065</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>711.5959595959596</v>
+        <v>422.892256548327</v>
       </c>
       <c r="C23" t="n">
-        <v>711.5959595959596</v>
+        <v>201.2007633735857</v>
       </c>
       <c r="D23" t="n">
-        <v>529.4351962223739</v>
+        <v>19.04</v>
       </c>
       <c r="E23" t="n">
-        <v>359.825732678018</v>
+        <v>19.04</v>
       </c>
       <c r="F23" t="n">
-        <v>183.1695420638646</v>
+        <v>19.04</v>
       </c>
       <c r="G23" t="n">
-        <v>183.1695420638646</v>
+        <v>19.04</v>
       </c>
       <c r="H23" t="n">
         <v>19.04</v>
@@ -5989,43 +5989,43 @@
         <v>538.1731939681143</v>
       </c>
       <c r="M23" t="n">
-        <v>538.1731939681144</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="N23" t="n">
-        <v>538.1731939681144</v>
+        <v>538.1731939681143</v>
       </c>
       <c r="O23" t="n">
-        <v>721.43204896916</v>
+        <v>721.4320489691598</v>
       </c>
       <c r="P23" t="n">
-        <v>936.910434554011</v>
+        <v>936.9104345540109</v>
       </c>
       <c r="Q23" t="n">
-        <v>936.910434554011</v>
+        <v>952</v>
       </c>
       <c r="R23" t="n">
         <v>952</v>
       </c>
       <c r="S23" t="n">
-        <v>952</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="T23" t="n">
-        <v>952</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="U23" t="n">
-        <v>711.5959595959596</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="V23" t="n">
-        <v>711.5959595959596</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="W23" t="n">
-        <v>711.5959595959596</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="X23" t="n">
-        <v>711.5959595959596</v>
+        <v>719.3616801550061</v>
       </c>
       <c r="Y23" t="n">
-        <v>711.5959595959596</v>
+        <v>663.2962969523674</v>
       </c>
     </row>
     <row r="24">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>434.7707226782088</v>
+        <v>114.3293390676638</v>
       </c>
       <c r="C24" t="n">
-        <v>434.7707226782088</v>
+        <v>114.3293390676638</v>
       </c>
       <c r="D24" t="n">
-        <v>434.7707226782088</v>
+        <v>114.3293390676638</v>
       </c>
       <c r="E24" t="n">
-        <v>320.9605234641556</v>
+        <v>114.3293390676638</v>
       </c>
       <c r="F24" t="n">
-        <v>210.2168443349871</v>
+        <v>114.3293390676638</v>
       </c>
       <c r="G24" t="n">
         <v>114.3293390676638</v>
@@ -6059,22 +6059,22 @@
         <v>19.04</v>
       </c>
       <c r="J24" t="n">
-        <v>19.04</v>
+        <v>221.353099534713</v>
       </c>
       <c r="K24" t="n">
-        <v>44.94542396075474</v>
+        <v>247.2585234954677</v>
       </c>
       <c r="L24" t="n">
-        <v>280.5654239607547</v>
+        <v>308.7095151086752</v>
       </c>
       <c r="M24" t="n">
-        <v>436.5656934687181</v>
+        <v>544.3295151086752</v>
       </c>
       <c r="N24" t="n">
-        <v>525.7855528747629</v>
+        <v>544.3295151086752</v>
       </c>
       <c r="O24" t="n">
-        <v>761.4055528747629</v>
+        <v>595.5227200361032</v>
       </c>
       <c r="P24" t="n">
         <v>810.2746335655219</v>
@@ -6083,28 +6083,28 @@
         <v>952</v>
       </c>
       <c r="R24" t="n">
-        <v>948.3652849044523</v>
+        <v>711.5959595959596</v>
       </c>
       <c r="S24" t="n">
-        <v>948.3652849044523</v>
+        <v>664.3600636540181</v>
       </c>
       <c r="T24" t="n">
-        <v>948.3652849044523</v>
+        <v>664.3600636540181</v>
       </c>
       <c r="U24" t="n">
-        <v>948.3652849044523</v>
+        <v>492.4842952665605</v>
       </c>
       <c r="V24" t="n">
-        <v>761.9908735998865</v>
+        <v>306.1098839619947</v>
       </c>
       <c r="W24" t="n">
-        <v>761.9908735998865</v>
+        <v>306.1098839619947</v>
       </c>
       <c r="X24" t="n">
-        <v>761.9908735998865</v>
+        <v>114.3293390676638</v>
       </c>
       <c r="Y24" t="n">
-        <v>590.8884566643973</v>
+        <v>114.3293390676638</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>132.8031328076327</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="C25" t="n">
-        <v>89.64631801162803</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="D25" t="n">
-        <v>33.54912805652148</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="E25" t="n">
-        <v>33.54912805652148</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="F25" t="n">
-        <v>33.54912805652148</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="G25" t="n">
+        <v>154.0916006476329</v>
+      </c>
+      <c r="H25" t="n">
+        <v>161.2921028562108</v>
+      </c>
+      <c r="I25" t="n">
+        <v>234.365061136556</v>
+      </c>
+      <c r="J25" t="n">
+        <v>469.985061136556</v>
+      </c>
+      <c r="K25" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="L25" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="M25" t="n">
+        <v>490.2442393357194</v>
+      </c>
+      <c r="N25" t="n">
+        <v>250.6971522091625</v>
+      </c>
+      <c r="O25" t="n">
         <v>19.04</v>
       </c>
-      <c r="H25" t="n">
-        <v>26.2405022085779</v>
-      </c>
-      <c r="I25" t="n">
-        <v>99.3134604889231</v>
-      </c>
-      <c r="J25" t="n">
-        <v>334.9334604889231</v>
-      </c>
-      <c r="K25" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="L25" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="M25" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="N25" t="n">
-        <v>355.1926386880866</v>
-      </c>
-      <c r="O25" t="n">
-        <v>355.1926386880866</v>
-      </c>
       <c r="P25" t="n">
-        <v>355.1926386880866</v>
+        <v>19.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>114.7885982840461</v>
+        <v>19.04</v>
       </c>
       <c r="R25" t="n">
-        <v>55.79734311905272</v>
+        <v>19.04</v>
       </c>
       <c r="S25" t="n">
-        <v>55.79734311905272</v>
+        <v>19.04</v>
       </c>
       <c r="T25" t="n">
-        <v>78.44872883523463</v>
+        <v>41.69138571618191</v>
       </c>
       <c r="U25" t="n">
-        <v>156.7366326210623</v>
+        <v>119.9792895020095</v>
       </c>
       <c r="V25" t="n">
-        <v>187.2580255070082</v>
+        <v>150.5006823879555</v>
       </c>
       <c r="W25" t="n">
-        <v>190.8489437666856</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="X25" t="n">
-        <v>190.8489437666856</v>
+        <v>154.0916006476329</v>
       </c>
       <c r="Y25" t="n">
-        <v>132.8031328076327</v>
+        <v>154.0916006476329</v>
       </c>
     </row>
     <row r="26">
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
       <c r="C26" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
       <c r="D26" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
       <c r="E26" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
       <c r="F26" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
       <c r="G26" t="n">
         <v>14.72</v>
@@ -6226,13 +6226,13 @@
         <v>471.6938749228882</v>
       </c>
       <c r="M26" t="n">
-        <v>371.6799999999998</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>371.6799999999998</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>553.8399999999999</v>
+        <v>553.84</v>
       </c>
       <c r="P26" t="n">
         <v>736</v>
@@ -6247,22 +6247,22 @@
         <v>550.1414141414141</v>
       </c>
       <c r="T26" t="n">
-        <v>364.2828282828281</v>
+        <v>364.2828282828282</v>
       </c>
       <c r="U26" t="n">
-        <v>364.2828282828281</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="V26" t="n">
-        <v>364.2828282828281</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="W26" t="n">
-        <v>364.2828282828281</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="X26" t="n">
-        <v>364.2828282828281</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="Y26" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="27">
@@ -6272,46 +6272,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>516.7776621808779</v>
+        <v>14.72</v>
       </c>
       <c r="C27" t="n">
-        <v>368.1918920338887</v>
+        <v>14.72</v>
       </c>
       <c r="D27" t="n">
-        <v>368.1918920338887</v>
+        <v>14.72</v>
       </c>
       <c r="E27" t="n">
-        <v>238.2200766582193</v>
+        <v>14.72</v>
       </c>
       <c r="F27" t="n">
-        <v>238.2200766582193</v>
+        <v>14.72</v>
       </c>
       <c r="G27" t="n">
-        <v>126.17095522928</v>
+        <v>14.72</v>
       </c>
       <c r="H27" t="n">
         <v>14.72</v>
       </c>
       <c r="I27" t="n">
-        <v>39.26502419398005</v>
+        <v>14.72</v>
       </c>
       <c r="J27" t="n">
-        <v>39.26502419398005</v>
+        <v>85.05835858551487</v>
       </c>
       <c r="K27" t="n">
-        <v>221.4250241939801</v>
+        <v>110.9637825462696</v>
       </c>
       <c r="L27" t="n">
-        <v>324.1822540537206</v>
+        <v>172.4147741594772</v>
       </c>
       <c r="M27" t="n">
-        <v>324.1822540537206</v>
+        <v>172.4147741594772</v>
       </c>
       <c r="N27" t="n">
-        <v>397.5621134597653</v>
+        <v>245.7946335655219</v>
       </c>
       <c r="O27" t="n">
-        <v>448.7553183871934</v>
+        <v>427.9546335655219</v>
       </c>
       <c r="P27" t="n">
         <v>610.1146335655219</v>
@@ -6320,28 +6320,28 @@
         <v>736</v>
       </c>
       <c r="R27" t="n">
-        <v>736</v>
+        <v>572.2957575757576</v>
       </c>
       <c r="S27" t="n">
-        <v>702.6362480394639</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="T27" t="n">
-        <v>516.7776621808779</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="U27" t="n">
-        <v>516.7776621808779</v>
+        <v>14.72</v>
       </c>
       <c r="V27" t="n">
-        <v>516.7776621808779</v>
+        <v>14.72</v>
       </c>
       <c r="W27" t="n">
-        <v>516.7776621808779</v>
+        <v>14.72</v>
       </c>
       <c r="X27" t="n">
-        <v>516.7776621808779</v>
+        <v>14.72</v>
       </c>
       <c r="Y27" t="n">
-        <v>516.7776621808779</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>98.6606823879555</v>
+        <v>44.01044088411471</v>
       </c>
       <c r="C28" t="n">
-        <v>98.6606823879555</v>
+        <v>44.01044088411471</v>
       </c>
       <c r="D28" t="n">
-        <v>98.6606823879555</v>
+        <v>23.5349145917989</v>
       </c>
       <c r="E28" t="n">
-        <v>98.6606823879555</v>
+        <v>23.5349145917989</v>
       </c>
       <c r="F28" t="n">
-        <v>98.6606823879555</v>
+        <v>23.5349145917989</v>
       </c>
       <c r="G28" t="n">
-        <v>98.6606823879555</v>
+        <v>23.5349145917989</v>
       </c>
       <c r="H28" t="n">
-        <v>98.6606823879555</v>
+        <v>14.72</v>
       </c>
       <c r="I28" t="n">
-        <v>155.8936406683007</v>
+        <v>71.95295828034521</v>
       </c>
       <c r="J28" t="n">
-        <v>338.0536406683007</v>
+        <v>254.1129582803452</v>
       </c>
       <c r="K28" t="n">
-        <v>342.4728188674642</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="L28" t="n">
-        <v>232.9025701901247</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="M28" t="n">
-        <v>152.6248395740053</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="N28" t="n">
-        <v>152.6248395740053</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="O28" t="n">
-        <v>152.6248395740053</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="P28" t="n">
-        <v>152.6248395740053</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="Q28" t="n">
-        <v>152.6248395740053</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="R28" t="n">
-        <v>152.6248395740053</v>
+        <v>258.5321364795087</v>
       </c>
       <c r="S28" t="n">
-        <v>14.72</v>
+        <v>120.6272969055033</v>
       </c>
       <c r="T28" t="n">
-        <v>21.53138571618191</v>
+        <v>127.4386826216852</v>
       </c>
       <c r="U28" t="n">
-        <v>83.97928950200954</v>
+        <v>189.8865864075129</v>
       </c>
       <c r="V28" t="n">
-        <v>98.6606823879555</v>
+        <v>204.5679792934588</v>
       </c>
       <c r="W28" t="n">
-        <v>98.6606823879555</v>
+        <v>192.0701915775905</v>
       </c>
       <c r="X28" t="n">
-        <v>98.6606823879555</v>
+        <v>192.0701915775905</v>
       </c>
       <c r="Y28" t="n">
-        <v>98.6606823879555</v>
+        <v>117.8627644569214</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="C29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="D29" t="n">
-        <v>364.2828282828282</v>
+        <v>736</v>
       </c>
       <c r="E29" t="n">
-        <v>200.5785858585859</v>
+        <v>566.7283299426525</v>
       </c>
       <c r="F29" t="n">
-        <v>14.72</v>
+        <v>380.8697440840666</v>
       </c>
       <c r="G29" t="n">
-        <v>14.72</v>
+        <v>195.0111582254807</v>
       </c>
       <c r="H29" t="n">
         <v>14.72</v>
@@ -6466,10 +6466,10 @@
         <v>406.9060854664082</v>
       </c>
       <c r="N29" t="n">
-        <v>371.6799999999998</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>553.8399999999999</v>
+        <v>553.84</v>
       </c>
       <c r="P29" t="n">
         <v>736</v>
@@ -6481,25 +6481,25 @@
         <v>736</v>
       </c>
       <c r="S29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="T29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="U29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="V29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="W29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="X29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="Y29" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
     </row>
     <row r="30">
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373.5106694841816</v>
+        <v>736</v>
       </c>
       <c r="C30" t="n">
-        <v>373.5106694841816</v>
+        <v>630.3877801506356</v>
       </c>
       <c r="D30" t="n">
-        <v>238.2200766582193</v>
+        <v>495.0971873246734</v>
       </c>
       <c r="E30" t="n">
-        <v>238.2200766582193</v>
+        <v>365.125371949004</v>
       </c>
       <c r="F30" t="n">
         <v>238.2200766582193</v>
@@ -6530,28 +6530,28 @@
         <v>14.72</v>
       </c>
       <c r="I30" t="n">
-        <v>21.71471812037627</v>
+        <v>14.72</v>
       </c>
       <c r="J30" t="n">
-        <v>131.8199432150684</v>
+        <v>137.0486390653062</v>
       </c>
       <c r="K30" t="n">
-        <v>157.7253671758232</v>
+        <v>162.9540630260609</v>
       </c>
       <c r="L30" t="n">
-        <v>339.8853671758231</v>
+        <v>224.4050546392685</v>
       </c>
       <c r="M30" t="n">
-        <v>339.8853671758231</v>
+        <v>305.7056934687182</v>
       </c>
       <c r="N30" t="n">
-        <v>413.2652265818679</v>
+        <v>379.0855528747629</v>
       </c>
       <c r="O30" t="n">
-        <v>595.4252265818679</v>
+        <v>561.2455528747629</v>
       </c>
       <c r="P30" t="n">
-        <v>736</v>
+        <v>610.1146335655219</v>
       </c>
       <c r="Q30" t="n">
         <v>736</v>
@@ -6566,19 +6566,19 @@
         <v>736</v>
       </c>
       <c r="U30" t="n">
-        <v>731.6486054905722</v>
+        <v>736</v>
       </c>
       <c r="V30" t="n">
-        <v>731.6486054905722</v>
+        <v>736</v>
       </c>
       <c r="W30" t="n">
-        <v>731.6486054905722</v>
+        <v>736</v>
       </c>
       <c r="X30" t="n">
-        <v>731.6486054905722</v>
+        <v>736</v>
       </c>
       <c r="Y30" t="n">
-        <v>545.7900196319863</v>
+        <v>736</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>86.97880611672271</v>
+        <v>86.16289467208713</v>
       </c>
       <c r="C31" t="n">
-        <v>86.97880611672271</v>
+        <v>86.16289467208713</v>
       </c>
       <c r="D31" t="n">
+        <v>86.16289467208713</v>
+      </c>
+      <c r="E31" t="n">
+        <v>86.16289467208713</v>
+      </c>
+      <c r="F31" t="n">
+        <v>86.16289467208713</v>
+      </c>
+      <c r="G31" t="n">
+        <v>86.16289467208713</v>
+      </c>
+      <c r="H31" t="n">
+        <v>77.34798008028824</v>
+      </c>
+      <c r="I31" t="n">
+        <v>134.5809383606334</v>
+      </c>
+      <c r="J31" t="n">
+        <v>316.7409383606334</v>
+      </c>
+      <c r="K31" t="n">
+        <v>321.1601165597969</v>
+      </c>
+      <c r="L31" t="n">
+        <v>321.1601165597969</v>
+      </c>
+      <c r="M31" t="n">
+        <v>321.1601165597969</v>
+      </c>
+      <c r="N31" t="n">
+        <v>321.1601165597969</v>
+      </c>
+      <c r="O31" t="n">
+        <v>135.301530701211</v>
+      </c>
+      <c r="P31" t="n">
         <v>14.72</v>
       </c>
-      <c r="E31" t="n">
+      <c r="Q31" t="n">
         <v>14.72</v>
       </c>
-      <c r="F31" t="n">
+      <c r="R31" t="n">
         <v>14.72</v>
       </c>
-      <c r="G31" t="n">
+      <c r="S31" t="n">
         <v>14.72</v>
       </c>
-      <c r="H31" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="I31" t="n">
-        <v>71.95295828034521</v>
-      </c>
-      <c r="J31" t="n">
-        <v>254.1129582803452</v>
-      </c>
-      <c r="K31" t="n">
-        <v>258.5321364795087</v>
-      </c>
-      <c r="L31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="M31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="N31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="O31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="P31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="R31" t="n">
-        <v>148.9618878021692</v>
-      </c>
-      <c r="S31" t="n">
-        <v>15.53591144463558</v>
-      </c>
       <c r="T31" t="n">
-        <v>22.34729716081749</v>
+        <v>21.53138571618191</v>
       </c>
       <c r="U31" t="n">
-        <v>84.79520094664511</v>
+        <v>83.97928950200954</v>
       </c>
       <c r="V31" t="n">
-        <v>99.47659383259108</v>
+        <v>98.6606823879555</v>
       </c>
       <c r="W31" t="n">
-        <v>86.97880611672271</v>
+        <v>86.16289467208713</v>
       </c>
       <c r="X31" t="n">
-        <v>86.97880611672271</v>
+        <v>86.16289467208713</v>
       </c>
       <c r="Y31" t="n">
-        <v>86.97880611672271</v>
+        <v>86.16289467208713</v>
       </c>
     </row>
     <row r="32">
@@ -6667,16 +6667,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>550.1414141414151</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="C32" t="n">
-        <v>550.1414141414151</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="D32" t="n">
-        <v>550.1414141414151</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="E32" t="n">
-        <v>379.8596430739656</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="F32" t="n">
         <v>194.0010572153797</v>
@@ -6700,43 +6700,43 @@
         <v>471.6938749228882</v>
       </c>
       <c r="M32" t="n">
-        <v>407.9161864765092</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>371.6800000000009</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>553.8400000000009</v>
+        <v>553.84</v>
       </c>
       <c r="P32" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="Q32" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="R32" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="S32" t="n">
-        <v>550.1414141414151</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="T32" t="n">
-        <v>550.1414141414151</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="U32" t="n">
-        <v>550.1414141414151</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="V32" t="n">
-        <v>550.1414141414151</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="W32" t="n">
-        <v>550.1414141414151</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="X32" t="n">
-        <v>550.1414141414151</v>
+        <v>379.8596430739656</v>
       </c>
       <c r="Y32" t="n">
-        <v>550.1414141414151</v>
+        <v>194.0010572153797</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>260.0395122346997</v>
+        <v>564.7307508622963</v>
       </c>
       <c r="C33" t="n">
-        <v>260.0395122346997</v>
+        <v>417.1550817254081</v>
       </c>
       <c r="D33" t="n">
-        <v>125.7590204188384</v>
+        <v>282.8745899095468</v>
       </c>
       <c r="E33" t="n">
-        <v>125.7590204188384</v>
+        <v>282.8745899095468</v>
       </c>
       <c r="F33" t="n">
-        <v>125.7590204188384</v>
+        <v>156.9793956288631</v>
       </c>
       <c r="G33" t="n">
-        <v>14.72</v>
+        <v>125.160854219179</v>
       </c>
       <c r="H33" t="n">
         <v>14.72</v>
       </c>
       <c r="I33" t="n">
-        <v>22.70471812037627</v>
+        <v>40.25502419398005</v>
       </c>
       <c r="J33" t="n">
-        <v>22.70471812037627</v>
+        <v>222.4150241939801</v>
       </c>
       <c r="K33" t="n">
-        <v>48.61014208113101</v>
+        <v>404.5750241939801</v>
       </c>
       <c r="L33" t="n">
-        <v>230.770142081131</v>
+        <v>466.0260158071877</v>
       </c>
       <c r="M33" t="n">
-        <v>266.1331615981839</v>
+        <v>466.0260158071877</v>
       </c>
       <c r="N33" t="n">
-        <v>340.5030210042287</v>
+        <v>466.0260158071877</v>
       </c>
       <c r="O33" t="n">
-        <v>409.8621901754248</v>
+        <v>543.1531094846649</v>
       </c>
       <c r="P33" t="n">
-        <v>592.0221901754248</v>
+        <v>592.0221901754239</v>
       </c>
       <c r="Q33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="R33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="S33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="T33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="U33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="V33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="W33" t="n">
-        <v>736.000000000001</v>
+        <v>736</v>
       </c>
       <c r="X33" t="n">
-        <v>550.1414141414151</v>
+        <v>736</v>
       </c>
       <c r="Y33" t="n">
-        <v>364.2828282828291</v>
+        <v>736</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>628.1039472503024</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="C34" t="n">
-        <v>628.1039472503024</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="D34" t="n">
-        <v>556.8552421436807</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="E34" t="n">
-        <v>490.2078635204923</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="F34" t="n">
-        <v>490.2078635204923</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="G34" t="n">
-        <v>490.2078635204923</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="H34" t="n">
-        <v>490.2078635204923</v>
+        <v>82.33818210049026</v>
       </c>
       <c r="I34" t="n">
-        <v>548.4308218008375</v>
+        <v>140.5611403808355</v>
       </c>
       <c r="J34" t="n">
-        <v>730.5908218008376</v>
+        <v>322.7211403808354</v>
       </c>
       <c r="K34" t="n">
-        <v>736.000000000001</v>
+        <v>328.1303185799989</v>
       </c>
       <c r="L34" t="n">
-        <v>627.4398523327626</v>
+        <v>328.1303185799989</v>
       </c>
       <c r="M34" t="n">
-        <v>627.4398523327626</v>
+        <v>328.1303185799989</v>
       </c>
       <c r="N34" t="n">
-        <v>627.4398523327626</v>
+        <v>151.6147385639043</v>
       </c>
       <c r="O34" t="n">
-        <v>627.4398523327626</v>
+        <v>151.6147385639043</v>
       </c>
       <c r="P34" t="n">
-        <v>627.4398523327626</v>
+        <v>151.6147385639043</v>
       </c>
       <c r="Q34" t="n">
-        <v>614.0354874250527</v>
+        <v>151.6147385639043</v>
       </c>
       <c r="R34" t="n">
-        <v>614.0354874250527</v>
+        <v>151.6147385639043</v>
       </c>
       <c r="S34" t="n">
-        <v>614.0354874250527</v>
+        <v>14.72</v>
       </c>
       <c r="T34" t="n">
-        <v>621.8368731412346</v>
+        <v>22.52138571618191</v>
       </c>
       <c r="U34" t="n">
-        <v>685.2747769270622</v>
+        <v>85.95928950200954</v>
       </c>
       <c r="V34" t="n">
-        <v>700.9461698130082</v>
+        <v>101.6306823879555</v>
       </c>
       <c r="W34" t="n">
-        <v>700.9461698130082</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="X34" t="n">
-        <v>700.9461698130082</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="Y34" t="n">
-        <v>700.9461698130082</v>
+        <v>90.14299568218814</v>
       </c>
     </row>
     <row r="35">
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>364.2828282828224</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="C35" t="n">
-        <v>178.4242424242332</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="D35" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="E35" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="F35" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="G35" t="n">
         <v>14.72</v>
@@ -6937,10 +6937,10 @@
         <v>471.6938749228882</v>
       </c>
       <c r="M35" t="n">
-        <v>407.9161864765092</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>371.68</v>
+        <v>371.6800000000001</v>
       </c>
       <c r="O35" t="n">
         <v>553.84</v>
@@ -6955,25 +6955,25 @@
         <v>736</v>
       </c>
       <c r="S35" t="n">
-        <v>736</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="T35" t="n">
-        <v>736</v>
+        <v>364.2828282828282</v>
       </c>
       <c r="U35" t="n">
-        <v>736</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="V35" t="n">
-        <v>736</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="W35" t="n">
-        <v>736</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="X35" t="n">
-        <v>736</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="Y35" t="n">
-        <v>550.1414141414114</v>
+        <v>200.5785858585859</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>269.576908646252</v>
+        <v>378.8721650037103</v>
       </c>
       <c r="C36" t="n">
-        <v>269.576908646252</v>
+        <v>231.2964958668221</v>
       </c>
       <c r="D36" t="n">
-        <v>269.576908646252</v>
+        <v>231.2964958668221</v>
       </c>
       <c r="E36" t="n">
-        <v>140.6151942806837</v>
+        <v>231.2964958668221</v>
       </c>
       <c r="F36" t="n">
-        <v>14.72</v>
+        <v>231.2964958668221</v>
       </c>
       <c r="G36" t="n">
-        <v>14.72</v>
+        <v>125.160854219179</v>
       </c>
       <c r="H36" t="n">
         <v>14.72</v>
@@ -7007,25 +7007,25 @@
         <v>40.25502419398005</v>
       </c>
       <c r="J36" t="n">
-        <v>191.0814969280825</v>
+        <v>222.4150241939801</v>
       </c>
       <c r="K36" t="n">
-        <v>373.2414969280825</v>
+        <v>404.5750241939801</v>
       </c>
       <c r="L36" t="n">
-        <v>434.6924885412901</v>
+        <v>466.0260158071877</v>
       </c>
       <c r="M36" t="n">
-        <v>434.6924885412901</v>
+        <v>466.0260158071877</v>
       </c>
       <c r="N36" t="n">
-        <v>509.0623479473348</v>
+        <v>466.0260158071877</v>
       </c>
       <c r="O36" t="n">
-        <v>560.2555528747629</v>
+        <v>543.1531094846649</v>
       </c>
       <c r="P36" t="n">
-        <v>609.1246335655219</v>
+        <v>592.0221901754239</v>
       </c>
       <c r="Q36" t="n">
         <v>736</v>
@@ -7040,19 +7040,19 @@
         <v>736</v>
       </c>
       <c r="U36" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="V36" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="W36" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="X36" t="n">
-        <v>440.8461577839557</v>
+        <v>736</v>
       </c>
       <c r="Y36" t="n">
-        <v>440.8461577839557</v>
+        <v>550.141414141414</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101.6306823879555</v>
+        <v>22.52481358169789</v>
       </c>
       <c r="C37" t="n">
-        <v>101.6306823879555</v>
+        <v>22.52481358169789</v>
       </c>
       <c r="D37" t="n">
-        <v>30.3819772813338</v>
+        <v>22.52481358169789</v>
       </c>
       <c r="E37" t="n">
-        <v>30.3819772813338</v>
+        <v>22.52481358169789</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3819772813338</v>
+        <v>22.52481358169789</v>
       </c>
       <c r="G37" t="n">
-        <v>30.3819772813338</v>
+        <v>22.52481358169789</v>
       </c>
       <c r="H37" t="n">
-        <v>30.3819772813338</v>
+        <v>14.72</v>
       </c>
       <c r="I37" t="n">
-        <v>88.60493556167901</v>
+        <v>72.94295828034521</v>
       </c>
       <c r="J37" t="n">
-        <v>270.764935561679</v>
+        <v>255.1029582803452</v>
       </c>
       <c r="K37" t="n">
-        <v>276.1741137608425</v>
+        <v>260.5121364795086</v>
       </c>
       <c r="L37" t="n">
-        <v>276.1741137608425</v>
+        <v>260.5121364795086</v>
       </c>
       <c r="M37" t="n">
-        <v>276.1741137608425</v>
+        <v>260.5121364795086</v>
       </c>
       <c r="N37" t="n">
-        <v>276.1741137608425</v>
+        <v>260.5121364795086</v>
       </c>
       <c r="O37" t="n">
-        <v>276.1741137608425</v>
+        <v>74.65355062092274</v>
       </c>
       <c r="P37" t="n">
-        <v>276.1741137608425</v>
+        <v>74.65355062092274</v>
       </c>
       <c r="Q37" t="n">
-        <v>276.1741137608425</v>
+        <v>74.65355062092274</v>
       </c>
       <c r="R37" t="n">
-        <v>151.6147385639043</v>
+        <v>19.94404046221548</v>
       </c>
       <c r="S37" t="n">
-        <v>14.72</v>
+        <v>19.94404046221548</v>
       </c>
       <c r="T37" t="n">
-        <v>22.52138571618191</v>
+        <v>27.74542617839739</v>
       </c>
       <c r="U37" t="n">
-        <v>85.95928950200954</v>
+        <v>91.18332996422501</v>
       </c>
       <c r="V37" t="n">
-        <v>101.6306823879555</v>
+        <v>106.854722850171</v>
       </c>
       <c r="W37" t="n">
-        <v>101.6306823879555</v>
+        <v>95.36703614440361</v>
       </c>
       <c r="X37" t="n">
-        <v>101.6306823879555</v>
+        <v>95.36703614440361</v>
       </c>
       <c r="Y37" t="n">
-        <v>101.6306823879555</v>
+        <v>95.36703614440361</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>386.4371717171717</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="C38" t="n">
-        <v>386.4371717171717</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="D38" t="n">
-        <v>200.5785858585859</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="E38" t="n">
-        <v>200.5785858585859</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="F38" t="n">
-        <v>14.72</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="G38" t="n">
-        <v>14.72</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="H38" t="n">
         <v>14.72</v>
@@ -7192,25 +7192,25 @@
         <v>736</v>
       </c>
       <c r="S38" t="n">
-        <v>550.1414141414141</v>
+        <v>736</v>
       </c>
       <c r="T38" t="n">
         <v>550.1414141414141</v>
       </c>
       <c r="U38" t="n">
-        <v>550.1414141414141</v>
+        <v>364.2828282828282</v>
       </c>
       <c r="V38" t="n">
-        <v>550.1414141414141</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="W38" t="n">
-        <v>550.1414141414141</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="X38" t="n">
-        <v>550.1414141414141</v>
+        <v>194.0010572153797</v>
       </c>
       <c r="Y38" t="n">
-        <v>550.1414141414141</v>
+        <v>194.0010572153797</v>
       </c>
     </row>
     <row r="39">
@@ -7241,22 +7241,22 @@
         <v>14.72</v>
       </c>
       <c r="I39" t="n">
-        <v>40.25502419398004</v>
+        <v>40.25502419398005</v>
       </c>
       <c r="J39" t="n">
-        <v>199.2668345046579</v>
+        <v>222.4150241939801</v>
       </c>
       <c r="K39" t="n">
-        <v>225.1722584654127</v>
+        <v>248.3204481547348</v>
       </c>
       <c r="L39" t="n">
-        <v>286.6232500786202</v>
+        <v>417.5900451511922</v>
       </c>
       <c r="M39" t="n">
-        <v>286.6232500786202</v>
+        <v>417.5900451511922</v>
       </c>
       <c r="N39" t="n">
-        <v>360.993109484665</v>
+        <v>491.9599045572369</v>
       </c>
       <c r="O39" t="n">
         <v>543.1531094846649</v>
@@ -7274,22 +7274,22 @@
         <v>736</v>
       </c>
       <c r="T39" t="n">
-        <v>550.141414141414</v>
+        <v>736</v>
       </c>
       <c r="U39" t="n">
-        <v>550.141414141414</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="V39" t="n">
-        <v>364.2828282828281</v>
+        <v>364.2828282828282</v>
       </c>
       <c r="W39" t="n">
-        <v>364.2828282828281</v>
+        <v>364.2828282828282</v>
       </c>
       <c r="X39" t="n">
-        <v>178.4242424242422</v>
+        <v>178.4242424242423</v>
       </c>
       <c r="Y39" t="n">
-        <v>178.4242424242422</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="40">
@@ -7299,52 +7299,52 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.78845982524979</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="C40" t="n">
-        <v>28.78845982524979</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="D40" t="n">
-        <v>28.78845982524979</v>
+        <v>71.15141062801351</v>
       </c>
       <c r="E40" t="n">
-        <v>28.78845982524979</v>
+        <v>71.15141062801351</v>
       </c>
       <c r="F40" t="n">
-        <v>28.78845982524979</v>
+        <v>71.15141062801351</v>
       </c>
       <c r="G40" t="n">
-        <v>28.78845982524979</v>
+        <v>71.15141062801351</v>
       </c>
       <c r="H40" t="n">
-        <v>28.78845982524979</v>
+        <v>63.34659704631562</v>
       </c>
       <c r="I40" t="n">
-        <v>87.01141810559501</v>
+        <v>121.5695553266608</v>
       </c>
       <c r="J40" t="n">
-        <v>269.171418105595</v>
+        <v>303.7295553266608</v>
       </c>
       <c r="K40" t="n">
-        <v>274.5805963047585</v>
+        <v>309.1387335258243</v>
       </c>
       <c r="L40" t="n">
         <v>200.5785858585859</v>
       </c>
       <c r="M40" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="N40" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="O40" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="P40" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="Q40" t="n">
-        <v>14.72</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="R40" t="n">
         <v>14.72</v>
@@ -7362,13 +7362,13 @@
         <v>101.6306823879555</v>
       </c>
       <c r="W40" t="n">
-        <v>101.6306823879555</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="X40" t="n">
-        <v>101.6306823879555</v>
+        <v>90.14299568218814</v>
       </c>
       <c r="Y40" t="n">
-        <v>101.6306823879555</v>
+        <v>90.14299568218814</v>
       </c>
     </row>
     <row r="41">
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>364.2828282828231</v>
+        <v>106.287518282596</v>
       </c>
       <c r="C41" t="n">
-        <v>292.1461041411839</v>
+        <v>106.287518282596</v>
       </c>
       <c r="D41" t="n">
         <v>106.287518282596</v>
@@ -7426,28 +7426,28 @@
         <v>736</v>
       </c>
       <c r="R41" t="n">
-        <v>736</v>
+        <v>579.7619401714096</v>
       </c>
       <c r="S41" t="n">
-        <v>736</v>
+        <v>393.9033543128237</v>
       </c>
       <c r="T41" t="n">
-        <v>736</v>
+        <v>292.1461041411819</v>
       </c>
       <c r="U41" t="n">
-        <v>736</v>
+        <v>292.1461041411819</v>
       </c>
       <c r="V41" t="n">
-        <v>550.1414141414115</v>
+        <v>106.287518282596</v>
       </c>
       <c r="W41" t="n">
-        <v>550.1414141414115</v>
+        <v>106.287518282596</v>
       </c>
       <c r="X41" t="n">
-        <v>550.1414141414115</v>
+        <v>106.287518282596</v>
       </c>
       <c r="Y41" t="n">
-        <v>364.2828282828231</v>
+        <v>106.287518282596</v>
       </c>
     </row>
     <row r="42">
@@ -7457,46 +7457,46 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="C42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="D42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="E42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="F42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="G42" t="n">
-        <v>295.0223546827628</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="H42" t="n">
-        <v>109.1637688241766</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="I42" t="n">
         <v>14.72</v>
       </c>
       <c r="J42" t="n">
-        <v>196.88</v>
+        <v>60.9652149493602</v>
       </c>
       <c r="K42" t="n">
-        <v>379.04</v>
+        <v>87.86063891011494</v>
       </c>
       <c r="L42" t="n">
-        <v>441.4809916132076</v>
+        <v>270.0206389101149</v>
       </c>
       <c r="M42" t="n">
-        <v>501.656795072572</v>
+        <v>452.1806389101149</v>
       </c>
       <c r="N42" t="n">
-        <v>501.656795072572</v>
+        <v>634.3406389101149</v>
       </c>
       <c r="O42" t="n">
-        <v>553.84</v>
+        <v>686.5238438375429</v>
       </c>
       <c r="P42" t="n">
         <v>736</v>
@@ -7514,19 +7514,19 @@
         <v>480.880940541349</v>
       </c>
       <c r="U42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="V42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="W42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="X42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="Y42" t="n">
-        <v>480.880940541349</v>
+        <v>386.4371717171717</v>
       </c>
     </row>
     <row r="43">
@@ -7536,16 +7536,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
       <c r="C43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
       <c r="D43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
       <c r="E43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
       <c r="F43" t="n">
         <v>14.72</v>
@@ -7599,13 +7599,13 @@
         <v>28.37750639015622</v>
       </c>
       <c r="W43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
       <c r="X43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
       <c r="Y43" t="n">
-        <v>14.72</v>
+        <v>28.37750639015622</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>393.9033543128234</v>
+        <v>579.7619401714096</v>
       </c>
       <c r="C44" t="n">
-        <v>393.9033543128234</v>
+        <v>478.0046899997677</v>
       </c>
       <c r="D44" t="n">
-        <v>393.9033543128234</v>
+        <v>478.0046899997677</v>
       </c>
       <c r="E44" t="n">
-        <v>393.9033543128234</v>
+        <v>478.0046899997677</v>
       </c>
       <c r="F44" t="n">
-        <v>208.0447684542354</v>
+        <v>292.1461041411819</v>
       </c>
       <c r="G44" t="n">
-        <v>208.0447684542354</v>
+        <v>106.287518282596</v>
       </c>
       <c r="H44" t="n">
         <v>106.287518282596</v>
@@ -7648,7 +7648,7 @@
         <v>471.6938749228882</v>
       </c>
       <c r="M44" t="n">
-        <v>371.6800000000001</v>
+        <v>471.6938749228883</v>
       </c>
       <c r="N44" t="n">
         <v>371.6800000000001</v>
@@ -7672,19 +7672,19 @@
         <v>579.7619401714096</v>
       </c>
       <c r="U44" t="n">
-        <v>393.9033543128234</v>
+        <v>579.7619401714096</v>
       </c>
       <c r="V44" t="n">
-        <v>393.9033543128234</v>
+        <v>579.7619401714096</v>
       </c>
       <c r="W44" t="n">
-        <v>393.9033543128234</v>
+        <v>579.7619401714096</v>
       </c>
       <c r="X44" t="n">
-        <v>393.9033543128234</v>
+        <v>579.7619401714096</v>
       </c>
       <c r="Y44" t="n">
-        <v>393.9033543128234</v>
+        <v>579.7619401714096</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="C45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="D45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="E45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="F45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="G45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
       <c r="H45" t="n">
-        <v>109.1637688241746</v>
+        <v>200.5785858585859</v>
       </c>
       <c r="I45" t="n">
         <v>14.72</v>
       </c>
       <c r="J45" t="n">
-        <v>14.72</v>
+        <v>180.8056384304922</v>
       </c>
       <c r="K45" t="n">
-        <v>196.88</v>
+        <v>207.7010623912469</v>
       </c>
       <c r="L45" t="n">
-        <v>258.8166519905661</v>
+        <v>270.1420540044545</v>
       </c>
       <c r="M45" t="n">
-        <v>440.9766519905661</v>
+        <v>452.3020540044545</v>
       </c>
       <c r="N45" t="n">
-        <v>623.1366519905661</v>
+        <v>634.4620540044544</v>
       </c>
       <c r="O45" t="n">
-        <v>686.140919309241</v>
+        <v>686.6452589318825</v>
       </c>
       <c r="P45" t="n">
         <v>736</v>
       </c>
       <c r="Q45" t="n">
-        <v>666.7395263999349</v>
+        <v>736</v>
       </c>
       <c r="R45" t="n">
-        <v>666.7395263999349</v>
+        <v>736</v>
       </c>
       <c r="S45" t="n">
-        <v>666.7395263999349</v>
+        <v>736</v>
       </c>
       <c r="T45" t="n">
-        <v>666.7395263999349</v>
+        <v>736</v>
       </c>
       <c r="U45" t="n">
-        <v>480.8809405413487</v>
+        <v>736</v>
       </c>
       <c r="V45" t="n">
-        <v>480.8809405413487</v>
+        <v>736</v>
       </c>
       <c r="W45" t="n">
-        <v>480.8809405413487</v>
+        <v>736</v>
       </c>
       <c r="X45" t="n">
-        <v>480.8809405413487</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="Y45" t="n">
-        <v>295.0223546827609</v>
+        <v>386.4371717171717</v>
       </c>
     </row>
     <row r="46">
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="C46" t="n">
         <v>14.72</v>
@@ -7809,40 +7809,40 @@
         <v>28.37750639015622</v>
       </c>
       <c r="N46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="O46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="P46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="R46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="S46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="T46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="U46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="V46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="W46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="X46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
       <c r="Y46" t="n">
-        <v>28.37750639015622</v>
+        <v>14.72</v>
       </c>
     </row>
   </sheetData>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>278.1399115619153</v>
+        <v>293.3818968608941</v>
       </c>
       <c r="N2" t="n">
-        <v>222.06259161002</v>
+        <v>206.8206063110412</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -8046,19 +8046,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>211.8329050901467</v>
       </c>
       <c r="L3" t="n">
         <v>175.9282912997903</v>
       </c>
       <c r="M3" t="n">
-        <v>417.2797782656032</v>
+        <v>179.2797782656032</v>
       </c>
       <c r="N3" t="n">
-        <v>277.2012494664546</v>
+        <v>139.8789298928841</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>163.4894144834237</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -8210,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>293.3818968608941</v>
+        <v>278.1399115619153</v>
       </c>
       <c r="N5" t="n">
-        <v>206.8206063110412</v>
+        <v>222.0625916100201</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8286,16 +8286,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>126.9609188808638</v>
+        <v>75.25061087336074</v>
       </c>
       <c r="M6" t="n">
         <v>417.2797782656032</v>
       </c>
       <c r="N6" t="n">
-        <v>139.8789298928841</v>
+        <v>377.8789298928841</v>
       </c>
       <c r="O6" t="n">
-        <v>186.2896919924969</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -8441,13 +8441,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>15.24198529897893</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>278.1399115619153</v>
+        <v>293.3818968608942</v>
       </c>
       <c r="N8" t="n">
         <v>206.8206063110412</v>
@@ -8517,10 +8517,10 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>25.64333380332025</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>211.8329050901467</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -8529,13 +8529,13 @@
         <v>417.2797782656032</v>
       </c>
       <c r="N9" t="n">
-        <v>254.4807515690097</v>
+        <v>377.8789298928841</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>75.25061087336086</v>
       </c>
       <c r="P9" t="n">
-        <v>188.6372922315566</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8687,7 +8687,7 @@
         <v>48.13991156191531</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>206.8206063110412</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>294.54111633436</v>
+        <v>279.0624908127114</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>17.72758189252907</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>344.2043222310423</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -8833,7 +8833,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J13" t="n">
-        <v>129.4048552990696</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>48.13991156191531</v>
       </c>
       <c r="N14" t="n">
-        <v>162.4145450638165</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8936,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>220.2167955646645</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>179.2797782656032</v>
+        <v>341.4899103441607</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J16" t="n">
-        <v>129.4048552990696</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -9173,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>220.2167955646645</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>254.9779922152048</v>
+        <v>359.2174922366897</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>194.6050650354615</v>
+        <v>63.38189686089424</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.157322518440196</v>
       </c>
       <c r="R20" t="n">
         <v>220.2167955646645</v>
@@ -9474,10 +9474,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>417.2797782656032</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>35.66486092866204</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -9544,7 +9544,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J22" t="n">
-        <v>129.4048552990696</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>70.99358432245862</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>235.4587808636433</v>
+        <v>287.4309746127515</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>336.8558080716268</v>
+        <v>187.2797782656032</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>167.5584170087471</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>236.2167955646645</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -9942,22 +9942,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>157.8329050901467</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>29.67405377655879</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>132.2896919924969</v>
       </c>
       <c r="P27" t="n">
-        <v>113.6264994823935</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>236.2167955646645</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -10185,19 +10185,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>179.2797782656032</v>
+        <v>47.40163566908765</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>132.2896919924969</v>
       </c>
       <c r="P30" t="n">
-        <v>92.63201285593242</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>87.70829760679334</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -10410,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -10419,10 +10419,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>121.9282912997903</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>42.36292728197432</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>70.80821268126871</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>235.2167955646645</v>
+        <v>270.9866345189295</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -10650,7 +10650,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>177.9933062620096</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -10729,7 +10729,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J37" t="n">
-        <v>90.40485529906958</v>
+        <v>90.40485529906961</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -10817,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>156.4168546780453</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -10832,7 +10832,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>235.2167955646645</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>157.487609318416</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J40" t="n">
-        <v>90.4048552990696</v>
+        <v>134.2003162992274</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.157322518440196</v>
+        <v>8.157322518440196</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,25 +11124,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>209.6433338033203</v>
+        <v>71.35567213600731</v>
       </c>
       <c r="K42" t="n">
-        <v>157.3423390524109</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>121.9282912997903</v>
       </c>
       <c r="M42" t="n">
-        <v>239.0634181235471</v>
+        <v>363.2797782656031</v>
       </c>
       <c r="N42" t="n">
-        <v>138.8789298928841</v>
+        <v>323.8789298928841</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>133.6372922315566</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>179.126175388256</v>
+        <v>278.1399115619153</v>
       </c>
       <c r="N44" t="n">
-        <v>206.8206063110412</v>
+        <v>107.8068701373819</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11361,22 +11361,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>24.64333380332025</v>
+        <v>193.4066049452315</v>
       </c>
       <c r="K45" t="n">
-        <v>156.8329050901467</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>362.2797782656032</v>
+        <v>362.2797782656031</v>
       </c>
       <c r="N45" t="n">
-        <v>323.8789298928841</v>
+        <v>322.8789298928841</v>
       </c>
       <c r="O45" t="n">
-        <v>10.93036605176456</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.241794397568981</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22566,16 +22566,16 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>180.0411395175086</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>236.3642919886453</v>
+        <v>176.1636371085849</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3734759809475463</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -22636,7 +22636,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27.28226457318285</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>14.06421795992696</v>
+        <v>49.72205404629779</v>
       </c>
       <c r="N4" t="n">
         <v>67.1516162552914</v>
@@ -22715,7 +22715,7 @@
         <v>205.2248153610644</v>
       </c>
       <c r="Q4" t="n">
-        <v>256.3714350993433</v>
+        <v>268.912266425598</v>
       </c>
       <c r="R4" t="n">
         <v>296.0342263418069</v>
@@ -22752,7 +22752,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -22803,10 +22803,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>180.0411395175086</v>
       </c>
       <c r="U5" t="n">
-        <v>166.5000439693161</v>
+        <v>35.93348269480157</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>49.72205404629756</v>
+        <v>14.06421795992696</v>
       </c>
       <c r="N7" t="n">
         <v>67.1516162552914</v>
@@ -22949,13 +22949,13 @@
         <v>144.3538263740969</v>
       </c>
       <c r="P7" t="n">
-        <v>205.2248153610644</v>
+        <v>192.6839840348098</v>
       </c>
       <c r="Q7" t="n">
         <v>268.912266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>296.0342263418069</v>
+        <v>344.2328937544324</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.024617953956749</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23001,7 +23001,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.241794397568981</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23037,19 +23037,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>176.4109425798134</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>180.0411395175086</v>
       </c>
       <c r="U8" t="n">
-        <v>11.10005031745487</v>
+        <v>249.1000503174549</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>0.3734759809475463</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -23077,7 +23077,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>319.54132275083</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -23165,7 +23165,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>156.1889310299543</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -23180,7 +23180,7 @@
         <v>14.06421795992696</v>
       </c>
       <c r="N10" t="n">
-        <v>54.61078492903674</v>
+        <v>67.1516162552914</v>
       </c>
       <c r="O10" t="n">
         <v>144.3538263740969</v>
@@ -23226,10 +23226,10 @@
         <v>251.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>219.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>180.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>174.3632896068686</v>
@@ -23277,19 +23277,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>350.0411395175086</v>
+        <v>112.0411395175086</v>
       </c>
       <c r="U11" t="n">
-        <v>419.1000503174549</v>
+        <v>181.1000503174549</v>
       </c>
       <c r="V11" t="n">
-        <v>344.3462947962116</v>
+        <v>182.5325608133679</v>
       </c>
       <c r="W11" t="n">
         <v>408.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>124.2818334606677</v>
+        <v>362.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>281.3174326828064</v>
@@ -23302,7 +23302,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>154.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -23365,13 +23365,13 @@
         <v>184.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>129.2164971498648</v>
+        <v>202.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>169.3913927661343</v>
+        <v>60.92856420710972</v>
       </c>
     </row>
     <row r="13">
@@ -23414,25 +23414,25 @@
         <v>92.47454619056604</v>
       </c>
       <c r="M13" t="n">
-        <v>75.2494284511214</v>
+        <v>184.064217959927</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>237.1516162552914</v>
       </c>
       <c r="O13" t="n">
         <v>314.3538263740969</v>
       </c>
       <c r="P13" t="n">
-        <v>375.2248153610644</v>
+        <v>137.2248153610644</v>
       </c>
       <c r="Q13" t="n">
-        <v>438.912266425598</v>
+        <v>210.4200694832357</v>
       </c>
       <c r="R13" t="n">
         <v>466.0342263418068</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>120.5257911782653</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23466,19 +23466,19 @@
         <v>219.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>180.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>174.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>174.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>172.241794397569</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>162.4882466432259</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,16 +23511,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>62.39856773763157</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>350.0411395175086</v>
+        <v>112.0411395175086</v>
       </c>
       <c r="U14" t="n">
-        <v>419.1000503174549</v>
+        <v>181.1000503174549</v>
       </c>
       <c r="V14" t="n">
-        <v>399.8510241668239</v>
+        <v>354.7743552109369</v>
       </c>
       <c r="W14" t="n">
         <v>408.3734759809475</v>
@@ -23529,7 +23529,7 @@
         <v>362.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>43.31743268280638</v>
+        <v>281.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -23539,7 +23539,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>154.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>131.0999124455193</v>
@@ -23548,10 +23548,10 @@
         <v>117.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>112.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>109.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -23587,16 +23587,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>266.9265142735114</v>
+        <v>160.8819798999375</v>
       </c>
       <c r="S15" t="n">
-        <v>221.5017829834792</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>172.0892463495893</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>170.157010703583</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -23605,10 +23605,10 @@
         <v>202.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>134.1130426445889</v>
+        <v>169.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -23624,10 +23624,10 @@
         <v>42.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>55.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>50.98090483695654</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -23648,10 +23648,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>92.47454619056604</v>
+        <v>91.58103943116411</v>
       </c>
       <c r="M16" t="n">
-        <v>163.0889689825724</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>17.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>57.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23700,19 +23700,19 @@
         <v>251.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>219.4745782429939</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>174.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>61.31475708842463</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>172.241794397569</v>
       </c>
       <c r="H17" t="n">
         <v>162.4882466432259</v>
@@ -23754,13 +23754,13 @@
         <v>350.0411395175086</v>
       </c>
       <c r="U17" t="n">
-        <v>419.1000503174549</v>
+        <v>263.0617243721852</v>
       </c>
       <c r="V17" t="n">
-        <v>161.8510241668239</v>
+        <v>399.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>408.3734759809475</v>
+        <v>170.3734759809475</v>
       </c>
       <c r="X17" t="n">
         <v>362.2818334606677</v>
@@ -23779,19 +23779,19 @@
         <v>154.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>131.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>117.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>112.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>94.92863021464998</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -23824,16 +23824,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>266.9265142735114</v>
+        <v>94.30899960611995</v>
       </c>
       <c r="S18" t="n">
-        <v>221.5017829834792</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>112.9425897250776</v>
+        <v>172.0892463495893</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>170.157010703583</v>
       </c>
       <c r="V18" t="n">
         <v>184.5106671915202</v>
@@ -23842,10 +23842,10 @@
         <v>202.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>189.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>169.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -23858,13 +23858,13 @@
         <v>57.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>42.72524664804467</v>
       </c>
       <c r="D19" t="n">
         <v>55.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>50.98090483695654</v>
       </c>
       <c r="F19" t="n">
         <v>44.38285596774193</v>
@@ -23885,10 +23885,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>92.47454619056604</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>184.064217959927</v>
       </c>
       <c r="N19" t="n">
         <v>237.1516162552914</v>
@@ -23897,16 +23897,16 @@
         <v>314.3538263740969</v>
       </c>
       <c r="P19" t="n">
-        <v>375.2248153610644</v>
+        <v>146.7326184187022</v>
       </c>
       <c r="Q19" t="n">
-        <v>438.912266425598</v>
+        <v>200.912266425598</v>
       </c>
       <c r="R19" t="n">
         <v>466.0342263418068</v>
       </c>
       <c r="S19" t="n">
-        <v>81.74386272085962</v>
+        <v>120.5257911782653</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>17.44364543010755</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>57.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -23934,25 +23934,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>251.9993129555745</v>
+        <v>13.99931295557451</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>219.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>180.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>174.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>174.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>67.43879678064475</v>
       </c>
       <c r="H20" t="n">
-        <v>162.4882466432259</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23988,13 +23988,13 @@
         <v>230.311936646544</v>
       </c>
       <c r="T20" t="n">
-        <v>112.0411395175086</v>
+        <v>350.0411395175086</v>
       </c>
       <c r="U20" t="n">
         <v>419.1000503174549</v>
       </c>
       <c r="V20" t="n">
-        <v>280.8266255153987</v>
+        <v>399.8510241668239</v>
       </c>
       <c r="W20" t="n">
         <v>408.3734759809475</v>
@@ -24003,7 +24003,7 @@
         <v>362.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>281.3174326828064</v>
+        <v>43.31743268280638</v>
       </c>
     </row>
     <row r="21">
@@ -24013,16 +24013,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>154.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>131.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>117.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>109.6362423378769</v>
@@ -24067,10 +24067,10 @@
         <v>221.5017829834792</v>
       </c>
       <c r="T21" t="n">
-        <v>3.127701130442048</v>
+        <v>172.0892463495893</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>75.94787919847097</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -24079,7 +24079,7 @@
         <v>202.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>189.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -24092,16 +24092,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>57.11380033707866</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>42.72524664804467</v>
       </c>
       <c r="D22" t="n">
         <v>55.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>50.98090483695654</v>
       </c>
       <c r="F22" t="n">
         <v>44.38285596774193</v>
@@ -24122,10 +24122,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>92.47454619056604</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>184.064217959927</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>237.1516162552914</v>
@@ -24137,13 +24137,13 @@
         <v>375.2248153610644</v>
       </c>
       <c r="Q22" t="n">
-        <v>200.912266425598</v>
+        <v>438.912266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>388.3619812215244</v>
+        <v>466.0342263418068</v>
       </c>
       <c r="S22" t="n">
-        <v>120.5257911782653</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24158,10 +24158,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>17.44364543010755</v>
+        <v>5.481356665965993</v>
       </c>
       <c r="Y22" t="n">
-        <v>57.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -24171,25 +24171,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>251.9993129555745</v>
+        <v>13.99931295557451</v>
       </c>
       <c r="C23" t="n">
-        <v>219.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>6.449920697956316</v>
+        <v>174.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>174.8896287080119</v>
       </c>
       <c r="G23" t="n">
         <v>172.241794397569</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>162.4882466432259</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24222,13 +24222,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>230.311936646544</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>350.0411395175086</v>
       </c>
       <c r="U23" t="n">
-        <v>181.1000503174549</v>
+        <v>419.1000503174549</v>
       </c>
       <c r="V23" t="n">
         <v>399.8510241668239</v>
@@ -24240,7 +24240,7 @@
         <v>362.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>281.3174326828064</v>
+        <v>225.8127033121941</v>
       </c>
     </row>
     <row r="24">
@@ -24250,7 +24250,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>154.5565566463266</v>
       </c>
       <c r="C24" t="n">
         <v>131.0999124455193</v>
@@ -24259,13 +24259,13 @@
         <v>117.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>112.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>109.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>94.92863021464998</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -24298,16 +24298,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>263.3281463289192</v>
+        <v>28.92651427351137</v>
       </c>
       <c r="S24" t="n">
-        <v>221.5017829834792</v>
+        <v>174.7382460009571</v>
       </c>
       <c r="T24" t="n">
         <v>172.0892463495893</v>
       </c>
       <c r="U24" t="n">
-        <v>170.157010703583</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -24316,10 +24316,10 @@
         <v>202.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>189.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>169.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -24332,10 +24332,10 @@
         <v>57.11380033707866</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>42.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>55.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>50.98090483695654</v>
@@ -24344,7 +24344,7 @@
         <v>44.38285596774193</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>14.36403677595626</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -24365,19 +24365,19 @@
         <v>184.064217959927</v>
       </c>
       <c r="N25" t="n">
-        <v>237.1516162552914</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>314.3538263740969</v>
+        <v>85.01324568702609</v>
       </c>
       <c r="P25" t="n">
         <v>375.2248153610644</v>
       </c>
       <c r="Q25" t="n">
-        <v>200.912266425598</v>
+        <v>438.912266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>407.6328837284633</v>
+        <v>466.0342263418068</v>
       </c>
       <c r="S25" t="n">
         <v>120.5257911782653</v>
@@ -24398,7 +24398,7 @@
         <v>17.44364543010755</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>57.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -24423,7 +24423,7 @@
         <v>190.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>26.17459439756916</v>
+        <v>188.241794397569</v>
       </c>
       <c r="H26" t="n">
         <v>178.4882466432259</v>
@@ -24459,13 +24459,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>62.31193664654395</v>
+        <v>62.31193664654401</v>
       </c>
       <c r="T26" t="n">
-        <v>182.0411395175085</v>
+        <v>182.0411395175086</v>
       </c>
       <c r="U26" t="n">
-        <v>435.1000503174549</v>
+        <v>273.032850317455</v>
       </c>
       <c r="V26" t="n">
         <v>415.8510241668239</v>
@@ -24490,22 +24490,22 @@
         <v>170.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>147.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>133.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>128.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>125.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>110.92863021465</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>110.3364456769872</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24535,16 +24535,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>282.9265142735114</v>
+        <v>120.8593142735114</v>
       </c>
       <c r="S27" t="n">
-        <v>204.4716685425485</v>
+        <v>53.50178298347923</v>
       </c>
       <c r="T27" t="n">
-        <v>4.089246349589175</v>
+        <v>4.08924634958926</v>
       </c>
       <c r="U27" t="n">
-        <v>186.157010703583</v>
+        <v>2.157010703583003</v>
       </c>
       <c r="V27" t="n">
         <v>200.5106671915202</v>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>73.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>58.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>71.53621805555548</v>
+        <v>51.26544702616282</v>
       </c>
       <c r="E28" t="n">
         <v>66.98090483695654</v>
@@ -24584,7 +24584,7 @@
         <v>30.36403677595626</v>
       </c>
       <c r="H28" t="n">
-        <v>8.726765445880911</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>108.474546190566</v>
       </c>
       <c r="M28" t="n">
-        <v>120.5892646499688</v>
+        <v>200.064217959927</v>
       </c>
       <c r="N28" t="n">
         <v>253.1516162552914</v>
@@ -24629,13 +24629,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>12.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>33.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>73.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24651,19 +24651,19 @@
         <v>235.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>12.33915573984973</v>
+        <v>196.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>28.29608960686883</v>
+        <v>22.78433625009464</v>
       </c>
       <c r="F29" t="n">
-        <v>6.889628708011799</v>
+        <v>6.889628708011855</v>
       </c>
       <c r="G29" t="n">
-        <v>188.241794397569</v>
+        <v>4.241794397568976</v>
       </c>
       <c r="H29" t="n">
-        <v>178.4882466432259</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>62.31193664654395</v>
+        <v>246.311936646544</v>
       </c>
       <c r="T29" t="n">
         <v>366.0411395175086</v>
@@ -24724,19 +24724,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>170.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>147.0999124455193</v>
+        <v>42.54381479464858</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>128.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>125.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24781,7 +24781,7 @@
         <v>188.0892463495893</v>
       </c>
       <c r="U30" t="n">
-        <v>181.8491301392495</v>
+        <v>186.157010703583</v>
       </c>
       <c r="V30" t="n">
         <v>200.5106671915202</v>
@@ -24793,7 +24793,7 @@
         <v>205.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.391392766134345</v>
+        <v>185.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -24809,7 +24809,7 @@
         <v>58.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>71.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>66.98090483695654</v>
@@ -24821,7 +24821,7 @@
         <v>30.36403677595626</v>
       </c>
       <c r="H31" t="n">
-        <v>8.726765445880911</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>108.474546190566</v>
       </c>
       <c r="M31" t="n">
         <v>200.064217959927</v>
@@ -24842,10 +24842,10 @@
         <v>253.1516162552914</v>
       </c>
       <c r="O31" t="n">
-        <v>330.3538263740969</v>
+        <v>146.3538263740969</v>
       </c>
       <c r="P31" t="n">
-        <v>391.2248153610644</v>
+        <v>271.8490999668655</v>
       </c>
       <c r="Q31" t="n">
         <v>454.912266425598</v>
@@ -24854,7 +24854,7 @@
         <v>482.0342263418068</v>
       </c>
       <c r="S31" t="n">
-        <v>4.434074584307012</v>
+        <v>136.5257911782653</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24891,10 +24891,10 @@
         <v>195.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>20.78433625009367</v>
+        <v>189.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>5.889628708011827</v>
+        <v>189.8896287080119</v>
       </c>
       <c r="G32" t="n">
         <v>187.241794397569</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>61.31193664654395</v>
+        <v>61.31193664654401</v>
       </c>
       <c r="T32" t="n">
         <v>365.0411395175086</v>
@@ -24948,10 +24948,10 @@
         <v>423.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>377.2818334606677</v>
+        <v>208.7028801038937</v>
       </c>
       <c r="Y32" t="n">
-        <v>296.3174326828064</v>
+        <v>112.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -24961,10 +24961,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66.35567375867848</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>146.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -24973,13 +24973,13 @@
         <v>127.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>124.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>78.42827421906271</v>
       </c>
       <c r="H33" t="n">
-        <v>109.3364456769872</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -25027,10 +25027,10 @@
         <v>217.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>20.86273944538755</v>
+        <v>204.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3913927661342096</v>
+        <v>184.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -25040,16 +25040,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>72.11380033707866</v>
       </c>
       <c r="C34" t="n">
         <v>57.72524664804467</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>70.53621805555548</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>65.98090483695654</v>
       </c>
       <c r="F34" t="n">
         <v>59.38285596774193</v>
@@ -25058,7 +25058,7 @@
         <v>29.36403677595626</v>
       </c>
       <c r="H34" t="n">
-        <v>7.726765445880911</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25070,13 +25070,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>107.474546190566</v>
       </c>
       <c r="M34" t="n">
         <v>199.064217959927</v>
       </c>
       <c r="N34" t="n">
-        <v>252.1516162552914</v>
+        <v>77.40119203935782</v>
       </c>
       <c r="O34" t="n">
         <v>329.3538263740969</v>
@@ -25085,13 +25085,13 @@
         <v>390.2248153610644</v>
       </c>
       <c r="Q34" t="n">
-        <v>440.6419451669652</v>
+        <v>453.912266425598</v>
       </c>
       <c r="R34" t="n">
         <v>481.0342263418068</v>
       </c>
       <c r="S34" t="n">
-        <v>135.5257911782653</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>11.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>32.44364543010755</v>
@@ -25119,13 +25119,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>82.99931295557144</v>
+        <v>266.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>50.47457824299062</v>
+        <v>234.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>33.27195573985895</v>
+        <v>195.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>189.3632896068686</v>
@@ -25134,7 +25134,7 @@
         <v>189.8896287080119</v>
       </c>
       <c r="G35" t="n">
-        <v>187.241794397569</v>
+        <v>3.241794397568975</v>
       </c>
       <c r="H35" t="n">
         <v>177.4882466432259</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>245.311936646544</v>
+        <v>61.31193664654401</v>
       </c>
       <c r="T35" t="n">
-        <v>365.0411395175086</v>
+        <v>181.0411395175086</v>
       </c>
       <c r="U35" t="n">
-        <v>434.1000503174549</v>
+        <v>272.032850317455</v>
       </c>
       <c r="V35" t="n">
         <v>414.8510241668239</v>
@@ -25188,7 +25188,7 @@
         <v>377.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>112.3174326828037</v>
+        <v>296.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -25201,22 +25201,22 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>146.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>132.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>127.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>124.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>109.92863021465</v>
+        <v>4.854344983483287</v>
       </c>
       <c r="H36" t="n">
-        <v>109.3364456769872</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25255,7 +25255,7 @@
         <v>187.0892463495893</v>
       </c>
       <c r="U36" t="n">
-        <v>1.157010703582974</v>
+        <v>185.157010703583</v>
       </c>
       <c r="V36" t="n">
         <v>199.5106671915202</v>
@@ -25264,10 +25264,10 @@
         <v>217.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>96.66043565150378</v>
+        <v>204.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>184.3913927661343</v>
+        <v>0.3913927661342096</v>
       </c>
     </row>
     <row r="37">
@@ -25277,13 +25277,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>72.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>57.72524664804467</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>70.53621805555548</v>
       </c>
       <c r="E37" t="n">
         <v>65.98090483695654</v>
@@ -25295,7 +25295,7 @@
         <v>29.36403677595626</v>
       </c>
       <c r="H37" t="n">
-        <v>7.726765445880911</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -25316,7 +25316,7 @@
         <v>252.1516162552914</v>
       </c>
       <c r="O37" t="n">
-        <v>329.3538263740969</v>
+        <v>145.3538263740969</v>
       </c>
       <c r="P37" t="n">
         <v>390.2248153610644</v>
@@ -25325,10 +25325,10 @@
         <v>453.912266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>357.720444896838</v>
+        <v>426.8718112846866</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>135.5257911782653</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25340,7 +25340,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>11.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>32.44364543010755</v>
@@ -25356,25 +25356,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>104.9321129555746</v>
+        <v>266.9993129555745</v>
       </c>
       <c r="C38" t="n">
         <v>234.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>11.33915573984979</v>
+        <v>195.3391557398498</v>
       </c>
       <c r="E38" t="n">
         <v>189.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>5.889628708011855</v>
+        <v>189.8896287080119</v>
       </c>
       <c r="G38" t="n">
         <v>187.241794397569</v>
       </c>
       <c r="H38" t="n">
-        <v>177.4882466432259</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,16 +25407,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>61.31193664654398</v>
+        <v>245.311936646544</v>
       </c>
       <c r="T38" t="n">
-        <v>365.0411395175086</v>
+        <v>181.0411395175086</v>
       </c>
       <c r="U38" t="n">
-        <v>434.1000503174549</v>
+        <v>250.1000503174549</v>
       </c>
       <c r="V38" t="n">
-        <v>414.8510241668239</v>
+        <v>246.2720708100499</v>
       </c>
       <c r="W38" t="n">
         <v>423.3734759809475</v>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.489356646326854</v>
+        <v>169.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>146.0999124455193</v>
@@ -25489,22 +25489,22 @@
         <v>236.5017829834792</v>
       </c>
       <c r="T39" t="n">
-        <v>3.089246349589075</v>
+        <v>187.0892463495893</v>
       </c>
       <c r="U39" t="n">
-        <v>185.157010703583</v>
+        <v>1.157010703583003</v>
       </c>
       <c r="V39" t="n">
-        <v>15.51066719152016</v>
+        <v>15.51066719152018</v>
       </c>
       <c r="W39" t="n">
         <v>217.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>20.86273944538755</v>
+        <v>20.86273944538758</v>
       </c>
       <c r="Y39" t="n">
-        <v>184.3913927661343</v>
+        <v>22.32419276613447</v>
       </c>
     </row>
     <row r="40">
@@ -25514,13 +25514,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>72.11380033707866</v>
       </c>
       <c r="C40" t="n">
         <v>57.72524664804467</v>
       </c>
       <c r="D40" t="n">
-        <v>70.53621805555548</v>
+        <v>51.7345488519226</v>
       </c>
       <c r="E40" t="n">
         <v>65.98090483695654</v>
@@ -25529,10 +25529,10 @@
         <v>59.38285596774193</v>
       </c>
       <c r="G40" t="n">
-        <v>29.36403677595627</v>
+        <v>29.36403677595626</v>
       </c>
       <c r="H40" t="n">
-        <v>7.726765445880915</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -25544,10 +25544,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>34.21255584885516</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>15.06421795992696</v>
+        <v>199.064217959927</v>
       </c>
       <c r="N40" t="n">
         <v>252.1516162552914</v>
@@ -25562,7 +25562,7 @@
         <v>453.912266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>481.0342263418069</v>
+        <v>297.0342263418068</v>
       </c>
       <c r="S40" t="n">
         <v>135.5257911782653</v>
@@ -25577,7 +25577,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>11.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>32.44364543010755</v>
@@ -25596,10 +25596,10 @@
         <v>480.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>377.0592213427711</v>
+        <v>448.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>225.3391557398477</v>
+        <v>409.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>403.3632896068686</v>
@@ -25641,19 +25641,19 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>154.6756792303045</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>459.311936646544</v>
+        <v>275.311936646544</v>
       </c>
       <c r="T41" t="n">
-        <v>579.0411395175086</v>
+        <v>478.3014618475831</v>
       </c>
       <c r="U41" t="n">
         <v>648.1000503174549</v>
       </c>
       <c r="V41" t="n">
-        <v>444.8510241668213</v>
+        <v>444.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>637.3734759809475</v>
@@ -25662,7 +25662,7 @@
         <v>591.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>326.3174326828039</v>
+        <v>510.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25687,13 +25687,13 @@
         <v>338.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>139.9286302146497</v>
+        <v>323.92863021465</v>
       </c>
       <c r="H42" t="n">
-        <v>139.3364456769869</v>
+        <v>139.3364456769872</v>
       </c>
       <c r="I42" t="n">
-        <v>94.70771513277219</v>
+        <v>4.207046268707018</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25729,7 +25729,7 @@
         <v>401.0892463495893</v>
       </c>
       <c r="U42" t="n">
-        <v>399.157010703583</v>
+        <v>305.6576795676475</v>
       </c>
       <c r="V42" t="n">
         <v>413.5106671915202</v>
@@ -25763,7 +25763,7 @@
         <v>279.9809048369565</v>
       </c>
       <c r="F43" t="n">
-        <v>273.3828559677419</v>
+        <v>259.8619246414873</v>
       </c>
       <c r="G43" t="n">
         <v>243.3640367759563</v>
@@ -25814,7 +25814,7 @@
         <v>198.1703102162162</v>
       </c>
       <c r="W43" t="n">
-        <v>211.851878512455</v>
+        <v>225.3728098387097</v>
       </c>
       <c r="X43" t="n">
         <v>246.4436454301076</v>
@@ -25833,7 +25833,7 @@
         <v>480.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>448.4745782429939</v>
+        <v>347.7349005730684</v>
       </c>
       <c r="D44" t="n">
         <v>409.3391557398498</v>
@@ -25842,13 +25842,13 @@
         <v>403.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>219.8896287080098</v>
+        <v>219.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>401.241794397569</v>
+        <v>217.241794397569</v>
       </c>
       <c r="H44" t="n">
-        <v>290.7485689733029</v>
+        <v>391.4882466432259</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25887,7 +25887,7 @@
         <v>579.0411395175086</v>
       </c>
       <c r="U44" t="n">
-        <v>464.1000503174545</v>
+        <v>648.1000503174549</v>
       </c>
       <c r="V44" t="n">
         <v>628.8510241668239</v>
@@ -25927,10 +25927,10 @@
         <v>323.92863021465</v>
       </c>
       <c r="H45" t="n">
-        <v>139.3364456769868</v>
+        <v>139.3364456769872</v>
       </c>
       <c r="I45" t="n">
-        <v>94.70771513277414</v>
+        <v>4.207046268707018</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>68.56786886406448</v>
       </c>
       <c r="R45" t="n">
         <v>495.9265142735114</v>
@@ -25966,7 +25966,7 @@
         <v>401.0892463495893</v>
       </c>
       <c r="U45" t="n">
-        <v>215.1570107035827</v>
+        <v>399.157010703583</v>
       </c>
       <c r="V45" t="n">
         <v>413.5106671915202</v>
@@ -25975,10 +25975,10 @@
         <v>431.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>418.8627394453875</v>
+        <v>234.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>214.3913927661324</v>
+        <v>236.3241927661344</v>
       </c>
     </row>
     <row r="46">
@@ -25991,7 +25991,7 @@
         <v>286.1138003370787</v>
       </c>
       <c r="C46" t="n">
-        <v>258.20431532179</v>
+        <v>271.7252466480447</v>
       </c>
       <c r="D46" t="n">
         <v>284.5362180555555</v>
@@ -26024,7 +26024,7 @@
         <v>413.064217959927</v>
       </c>
       <c r="N46" t="n">
-        <v>466.1516162552914</v>
+        <v>452.6306849290368</v>
       </c>
       <c r="O46" t="n">
         <v>543.3538263740969</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3396251.143711363</v>
+        <v>3396251.143711364</v>
       </c>
     </row>
     <row r="6">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4774353.22881118</v>
+        <v>4774353.228811179</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5463404.271361085</v>
+        <v>5463404.271361084</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6782624.676813165</v>
+        <v>6782624.676813168</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7423951.789895199</v>
+        <v>7423951.789895202</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8067533.025071869</v>
+        <v>8067533.025071871</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8710585.147153905</v>
+        <v>8710585.147153907</v>
       </c>
     </row>
     <row r="14">
@@ -26281,34 +26281,34 @@
         <v>918734.723399877</v>
       </c>
       <c r="F2" t="n">
+        <v>918734.723399877</v>
+      </c>
+      <c r="G2" t="n">
+        <v>918734.7233998766</v>
+      </c>
+      <c r="H2" t="n">
         <v>918734.7233998768</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>918734.7233998768</v>
       </c>
-      <c r="H2" t="n">
-        <v>918734.7233998766</v>
-      </c>
-      <c r="I2" t="n">
-        <v>918734.7233998767</v>
-      </c>
       <c r="J2" t="n">
-        <v>855102.8174427202</v>
+        <v>855102.8174427205</v>
       </c>
       <c r="K2" t="n">
-        <v>855102.8174427203</v>
+        <v>855102.8174427208</v>
       </c>
       <c r="L2" t="n">
-        <v>857402.8294427206</v>
+        <v>857402.8294427205</v>
       </c>
       <c r="M2" t="n">
         <v>857402.8294427205</v>
       </c>
       <c r="N2" t="n">
-        <v>857402.8294427202</v>
+        <v>857402.8294427206</v>
       </c>
       <c r="O2" t="n">
-        <v>330342.9085207914</v>
+        <v>330342.9085207915</v>
       </c>
       <c r="P2" t="n">
         <v>330342.9085207914</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>597777.8472795164</v>
+        <v>597664.4288244117</v>
       </c>
       <c r="C4" t="n">
-        <v>595871.0693123757</v>
+        <v>595757.6508572712</v>
       </c>
       <c r="D4" t="n">
-        <v>593961.70468191</v>
+        <v>593848.2862268054</v>
       </c>
       <c r="E4" t="n">
-        <v>410211.3696342112</v>
+        <v>410169.5198133887</v>
       </c>
       <c r="F4" t="n">
-        <v>408723.7954412241</v>
+        <v>408681.9456204016</v>
       </c>
       <c r="G4" t="n">
-        <v>407234.1684516628</v>
+        <v>407192.3186308403</v>
       </c>
       <c r="H4" t="n">
-        <v>405742.473944844</v>
+        <v>405700.6241240214</v>
       </c>
       <c r="I4" t="n">
-        <v>404248.6970082822</v>
+        <v>404206.8471874597</v>
       </c>
       <c r="J4" t="n">
-        <v>366701.0866666001</v>
+        <v>366669.5885001955</v>
       </c>
       <c r="K4" t="n">
-        <v>365307.3071611047</v>
+        <v>365275.8089947002</v>
       </c>
       <c r="L4" t="n">
-        <v>365408.0435521328</v>
+        <v>365376.0544986035</v>
       </c>
       <c r="M4" t="n">
-        <v>364006.1886170357</v>
+        <v>363974.1995635065</v>
       </c>
       <c r="N4" t="n">
-        <v>362602.3180476498</v>
+        <v>362570.3289941206</v>
       </c>
       <c r="O4" t="n">
-        <v>105923.2574494401</v>
+        <v>105826.4769842578</v>
       </c>
       <c r="P4" t="n">
-        <v>105916.697499906</v>
+        <v>105819.9170347238</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77706.27917812669</v>
+        <v>77819.69763323161</v>
       </c>
       <c r="C6" t="n">
-        <v>530964.0571452674</v>
+        <v>531077.4756003722</v>
       </c>
       <c r="D6" t="n">
-        <v>532873.4217757329</v>
+        <v>532986.8402308372</v>
       </c>
       <c r="E6" t="n">
-        <v>282498.4837656658</v>
+        <v>282540.3335864883</v>
       </c>
       <c r="F6" t="n">
-        <v>467986.0579586527</v>
+        <v>468027.9077794754</v>
       </c>
       <c r="G6" t="n">
-        <v>469475.6849482141</v>
+        <v>469517.5347690363</v>
       </c>
       <c r="H6" t="n">
-        <v>470967.3794550326</v>
+        <v>471009.2292758554</v>
       </c>
       <c r="I6" t="n">
-        <v>472461.1563915946</v>
+        <v>472503.0062124172</v>
       </c>
       <c r="J6" t="n">
-        <v>215037.1647761201</v>
+        <v>215068.662942525</v>
       </c>
       <c r="K6" t="n">
-        <v>452398.9442816155</v>
+        <v>452430.4424480206</v>
       </c>
       <c r="L6" t="n">
-        <v>453714.1508905878</v>
+        <v>453746.1399441171</v>
       </c>
       <c r="M6" t="n">
-        <v>455916.0058256848</v>
+        <v>455947.994879214</v>
       </c>
       <c r="N6" t="n">
-        <v>457319.8763950703</v>
+        <v>457351.8654486</v>
       </c>
       <c r="O6" t="n">
-        <v>204929.7820713514</v>
+        <v>205026.5625365337</v>
       </c>
       <c r="P6" t="n">
-        <v>204936.3420208854</v>
+        <v>205033.1224860677</v>
       </c>
     </row>
   </sheetData>
@@ -27008,10 +27008,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27112,10 +27112,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>101.6362423378769</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>88.21198463113771</v>
+        <v>86.92863021464998</v>
       </c>
       <c r="H3" t="n">
-        <v>324.3364456769872</v>
+        <v>266.1146993588868</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>189.207046268707</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>69.56786886406448</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>213.5017829834792</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27572,7 +27572,7 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>176.5106671915202</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27624,7 +27624,7 @@
         <v>322.4745461905661</v>
       </c>
       <c r="M4" t="n">
-        <v>400</v>
+        <v>364.3421639136292</v>
       </c>
       <c r="N4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>350.5257911782653</v>
+        <v>337.9849598520106</v>
       </c>
       <c r="T4" t="n">
         <v>207.1198124078971</v>
@@ -27767,7 +27767,7 @@
         <v>324.92863021465</v>
       </c>
       <c r="H6" t="n">
-        <v>238.7560539494401</v>
+        <v>86.33644567698718</v>
       </c>
       <c r="I6" t="n">
         <v>189.207046268707</v>
@@ -27797,10 +27797,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>258.9265142735114</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>213.5017829834792</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>176.5106671915202</v>
+        <v>206.985429811135</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>194.3731429098285</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>274.572969010824</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27861,7 +27861,7 @@
         <v>322.4745461905661</v>
       </c>
       <c r="M7" t="n">
-        <v>364.3421639136294</v>
+        <v>400</v>
       </c>
       <c r="N7" t="n">
         <v>400</v>
@@ -27876,7 +27876,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>400</v>
+        <v>351.8013325873744</v>
       </c>
       <c r="S7" t="n">
         <v>350.5257911782653</v>
@@ -27958,7 +27958,7 @@
         <v>155.6756792303045</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>283.9009940667306</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>396.7643603542971</v>
       </c>
     </row>
     <row r="9">
@@ -27989,16 +27989,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>123.0999124455193</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>104.6720972219126</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>20.0949195870469</v>
+        <v>101.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>324.92863021465</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>258.9265142735114</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>213.5017829834792</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28046,7 +28046,7 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>328.930275463973</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>238.7499654870979</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28086,7 +28086,7 @@
         <v>222.7267654458809</v>
       </c>
       <c r="I10" t="n">
-        <v>156.1889310299543</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -28095,7 +28095,7 @@
         <v>209.5361836372086</v>
       </c>
       <c r="L10" t="n">
-        <v>322.4745461905661</v>
+        <v>309.9337148643114</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>230</v>
       </c>
       <c r="I11" t="n">
-        <v>227.5408441225292</v>
+        <v>212.2988588235503</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>230</v>
       </c>
       <c r="N11" t="n">
-        <v>206.8206063110412</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R11" t="n">
-        <v>155.6756792303045</v>
+        <v>186.3962900509321</v>
       </c>
       <c r="S11" t="n">
         <v>230</v>
@@ -28244,7 +28244,7 @@
         <v>230</v>
       </c>
       <c r="I12" t="n">
-        <v>230</v>
+        <v>206.9346281612361</v>
       </c>
       <c r="J12" t="n">
         <v>230</v>
@@ -28256,16 +28256,16 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>179.2797782656032</v>
+      </c>
+      <c r="N12" t="n">
         <v>230</v>
       </c>
-      <c r="N12" t="n">
-        <v>33.67460766184178</v>
-      </c>
       <c r="O12" t="n">
-        <v>76.0452415430572</v>
+        <v>126.8000546700746</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>188.6372922315566</v>
       </c>
       <c r="Q12" t="n">
         <v>230</v>
@@ -28326,7 +28326,7 @@
         <v>230</v>
       </c>
       <c r="J13" t="n">
-        <v>230</v>
+        <v>225.2045389998422</v>
       </c>
       <c r="K13" t="n">
         <v>230</v>
@@ -28405,7 +28405,7 @@
         <v>212.2988588235503</v>
       </c>
       <c r="J14" t="n">
-        <v>15.24198529897893</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28417,7 +28417,7 @@
         <v>230</v>
       </c>
       <c r="N14" t="n">
-        <v>44.40606124722469</v>
+        <v>206.8206063110412</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R14" t="n">
-        <v>230</v>
+        <v>170.9176645292834</v>
       </c>
       <c r="S14" t="n">
         <v>230</v>
@@ -28481,28 +28481,28 @@
         <v>230</v>
       </c>
       <c r="I15" t="n">
-        <v>230</v>
+        <v>189.207046268707</v>
       </c>
       <c r="J15" t="n">
         <v>230</v>
       </c>
       <c r="K15" t="n">
-        <v>211.8329050901467</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>63.26387462918706</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>75.78986792144246</v>
       </c>
       <c r="N15" t="n">
-        <v>230</v>
+        <v>139.8789298928841</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>167.5584170087471</v>
       </c>
       <c r="Q15" t="n">
         <v>230</v>
@@ -28563,7 +28563,7 @@
         <v>230</v>
       </c>
       <c r="J16" t="n">
-        <v>230</v>
+        <v>225.2045389998422</v>
       </c>
       <c r="K16" t="n">
         <v>230</v>
@@ -28639,13 +28639,13 @@
         <v>230</v>
       </c>
       <c r="I17" t="n">
-        <v>91.65184309977002</v>
+        <v>212.2988588235503</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>15.24198529897893</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R17" t="n">
-        <v>230</v>
+        <v>170.9176645292834</v>
       </c>
       <c r="S17" t="n">
         <v>230</v>
@@ -28733,13 +28733,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>139.8789298928841</v>
+        <v>230</v>
       </c>
       <c r="O18" t="n">
-        <v>100.8823436452916</v>
+        <v>112.4342610917807</v>
       </c>
       <c r="P18" t="n">
-        <v>188.6372922315566</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>230</v>
@@ -28876,7 +28876,7 @@
         <v>230</v>
       </c>
       <c r="I20" t="n">
-        <v>91.65184309977002</v>
+        <v>212.2988588235503</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28888,19 +28888,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>83.5348465264538</v>
+        <v>230</v>
       </c>
       <c r="N20" t="n">
         <v>206.8206063110412</v>
       </c>
       <c r="O20" t="n">
-        <v>15.24198529897885</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.157322518440196</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>230</v>
@@ -28955,28 +28955,28 @@
         <v>230</v>
       </c>
       <c r="I21" t="n">
-        <v>230</v>
+        <v>206.9346281612361</v>
       </c>
       <c r="J21" t="n">
-        <v>230</v>
+        <v>25.64333380332025</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>185.6253912129299</v>
       </c>
       <c r="L21" t="n">
-        <v>143.1355312040297</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>139.8789298928841</v>
+        <v>104.2140689642221</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>186.289691992497</v>
       </c>
       <c r="P21" t="n">
-        <v>188.6372922315566</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>230</v>
@@ -29037,7 +29037,7 @@
         <v>230</v>
       </c>
       <c r="J22" t="n">
-        <v>230</v>
+        <v>225.2045389998422</v>
       </c>
       <c r="K22" t="n">
         <v>230</v>
@@ -29113,7 +29113,7 @@
         <v>230</v>
       </c>
       <c r="I23" t="n">
-        <v>141.3052745010916</v>
+        <v>212.2988588235503</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29137,10 +29137,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.157322518440196</v>
+        <v>24.39930781741912</v>
       </c>
       <c r="R23" t="n">
-        <v>230</v>
+        <v>162.785820951913</v>
       </c>
       <c r="S23" t="n">
         <v>230</v>
@@ -29192,25 +29192,25 @@
         <v>230</v>
       </c>
       <c r="I24" t="n">
-        <v>206.9346281612361</v>
+        <v>189.207046268707</v>
       </c>
       <c r="J24" t="n">
-        <v>25.64333380332025</v>
+        <v>230</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>175.9282912997903</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="N24" t="n">
-        <v>230</v>
+        <v>139.8789298928841</v>
       </c>
       <c r="O24" t="n">
-        <v>186.2896919924969</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -29362,7 +29362,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>179.1261753882558</v>
+        <v>179.126175388256</v>
       </c>
       <c r="N26" t="n">
         <v>206.8206063110412</v>
@@ -29377,7 +29377,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R26" t="n">
-        <v>214</v>
+        <v>155.6756792303045</v>
       </c>
       <c r="S26" t="n">
         <v>214</v>
@@ -29429,19 +29429,19 @@
         <v>214</v>
       </c>
       <c r="I27" t="n">
-        <v>214</v>
+        <v>189.207046268707</v>
       </c>
       <c r="J27" t="n">
-        <v>25.64333380332025</v>
+        <v>96.69218085939586</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>41.7234729762959</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>179.2797782656032</v>
+        <v>149.6057244890444</v>
       </c>
       <c r="N27" t="n">
         <v>214</v>
@@ -29450,7 +29450,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>134.6372922315566</v>
       </c>
       <c r="Q27" t="n">
         <v>214</v>
@@ -29602,7 +29602,7 @@
         <v>214</v>
       </c>
       <c r="N29" t="n">
-        <v>171.946781699297</v>
+        <v>171.9467816992972</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R29" t="n">
-        <v>214</v>
+        <v>155.6756792303045</v>
       </c>
       <c r="S29" t="n">
         <v>214</v>
@@ -29666,31 +29666,31 @@
         <v>214</v>
       </c>
       <c r="I30" t="n">
+        <v>206.9346281612361</v>
+      </c>
+      <c r="J30" t="n">
+        <v>149.2076156874679</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>214</v>
-      </c>
-      <c r="J30" t="n">
-        <v>136.8607328888679</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>121.9282912997903</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>214</v>
       </c>
       <c r="O30" t="n">
-        <v>132.2896919924969</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>69.56786886406448</v>
+        <v>214</v>
       </c>
       <c r="R30" t="n">
         <v>214</v>
@@ -29824,7 +29824,7 @@
         <v>215</v>
       </c>
       <c r="I32" t="n">
-        <v>124.5905612167569</v>
+        <v>91.65184309977002</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29836,10 +29836,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>179.126175388256</v>
       </c>
       <c r="N32" t="n">
-        <v>170.9467816992981</v>
+        <v>206.8206063110412</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -29906,25 +29906,25 @@
         <v>215</v>
       </c>
       <c r="J33" t="n">
-        <v>25.64333380332025</v>
+        <v>209.6433338033203</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>157.8329050901467</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>136.9168509836288</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>139.8789298928841</v>
       </c>
       <c r="O33" t="n">
-        <v>18.34945883208901</v>
+        <v>26.19584722227198</v>
       </c>
       <c r="P33" t="n">
-        <v>134.6372922315566</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>215</v>
@@ -30061,7 +30061,7 @@
         <v>215</v>
       </c>
       <c r="I35" t="n">
-        <v>141.4906461422815</v>
+        <v>91.65184309977002</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30073,10 +30073,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>179.126175388256</v>
       </c>
       <c r="N35" t="n">
-        <v>170.9467816992972</v>
+        <v>206.8206063110412</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R35" t="n">
-        <v>215</v>
+        <v>179.230161045735</v>
       </c>
       <c r="S35" t="n">
         <v>215</v>
@@ -30143,7 +30143,7 @@
         <v>215</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>209.6433338033203</v>
       </c>
       <c r="K36" t="n">
         <v>157.8329050901467</v>
@@ -30155,10 +30155,10 @@
         <v>179.2797782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>139.8789298928841</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>26.19584722227198</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -30310,7 +30310,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>22.70932071021068</v>
+        <v>179.126175388256</v>
       </c>
       <c r="N38" t="n">
         <v>206.8206063110412</v>
@@ -30325,7 +30325,7 @@
         <v>9.157322518440196</v>
       </c>
       <c r="R38" t="n">
-        <v>215</v>
+        <v>155.6756792303045</v>
       </c>
       <c r="S38" t="n">
         <v>215</v>
@@ -30380,22 +30380,22 @@
         <v>215</v>
       </c>
       <c r="J39" t="n">
-        <v>186.2613240161262</v>
+        <v>209.6433338033203</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>108.9076822053028</v>
       </c>
       <c r="M39" t="n">
-        <v>179.2797782656032</v>
+        <v>21.7921689471872</v>
       </c>
       <c r="N39" t="n">
         <v>215</v>
       </c>
       <c r="O39" t="n">
-        <v>132.2896919924969</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -30459,7 +30459,7 @@
         <v>215</v>
       </c>
       <c r="J40" t="n">
-        <v>215</v>
+        <v>171.2045389998422</v>
       </c>
       <c r="K40" t="n">
         <v>215</v>
@@ -30559,7 +30559,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -30617,25 +30617,25 @@
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.4905660377358491</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>0.6132075471698113</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -30854,25 +30854,25 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4905660377358491</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0.4905660377358491</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -31580,7 +31580,7 @@
         <v>192.7871909547739</v>
       </c>
       <c r="L8" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>266.122216080402</v>
@@ -31817,7 +31817,7 @@
         <v>192.7871909547739</v>
       </c>
       <c r="L11" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>266.122216080402</v>
@@ -32054,7 +32054,7 @@
         <v>192.7871909547739</v>
       </c>
       <c r="L14" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>266.122216080402</v>
@@ -32291,7 +32291,7 @@
         <v>192.7871909547739</v>
       </c>
       <c r="L17" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>266.122216080402</v>
@@ -33011,10 +33011,10 @@
         <v>270.428351758794</v>
       </c>
       <c r="O26" t="n">
-        <v>254.2478695740925</v>
+        <v>254.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>184.2870600406815</v>
+        <v>184.2870600406814</v>
       </c>
       <c r="Q26" t="n">
         <v>163.6653618090452</v>
@@ -33248,10 +33248,10 @@
         <v>270.428351758794</v>
       </c>
       <c r="O29" t="n">
-        <v>254.2478695740925</v>
+        <v>254.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>184.2870600406815</v>
+        <v>184.2870600406814</v>
       </c>
       <c r="Q29" t="n">
         <v>163.6653618090452</v>
@@ -33485,10 +33485,10 @@
         <v>270.428351758794</v>
       </c>
       <c r="O32" t="n">
-        <v>254.2478695740925</v>
+        <v>254.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>184.2870600406815</v>
+        <v>184.2870600406814</v>
       </c>
       <c r="Q32" t="n">
         <v>163.6653618090452</v>
@@ -33722,7 +33722,7 @@
         <v>270.428351758794</v>
       </c>
       <c r="O35" t="n">
-        <v>254.2478695740925</v>
+        <v>254.2478695740924</v>
       </c>
       <c r="P35" t="n">
         <v>184.2870600406814</v>
@@ -34752,10 +34752,10 @@
         <v>238.0000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>15.24198529897881</v>
       </c>
       <c r="N2" t="n">
-        <v>15.24198529897881</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>185.1099545465106</v>
@@ -34825,19 +34825,19 @@
         <v>201.8214081244682</v>
       </c>
       <c r="K3" t="n">
-        <v>26.16709490985328</v>
+        <v>238</v>
       </c>
       <c r="L3" t="n">
         <v>238</v>
       </c>
       <c r="M3" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>137.3223195735704</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>51.71030800750304</v>
+        <v>215.1997224909267</v>
       </c>
       <c r="P3" t="n">
         <v>49.3627077684434</v>
@@ -34989,10 +34989,10 @@
         <v>238.0000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>15.24198529897881</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="O5" t="n">
         <v>185.1099545465106</v>
@@ -35065,16 +35065,16 @@
         <v>26.16709490985328</v>
       </c>
       <c r="L6" t="n">
-        <v>189.0326275810735</v>
+        <v>137.3223195735704</v>
       </c>
       <c r="M6" t="n">
         <v>238</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="O6" t="n">
-        <v>238</v>
+        <v>51.71030800750304</v>
       </c>
       <c r="P6" t="n">
         <v>49.3627077684434</v>
@@ -35220,13 +35220,13 @@
         <v>93.58977264938204</v>
       </c>
       <c r="K8" t="n">
-        <v>208.0291762537528</v>
+        <v>192.7871909547739</v>
       </c>
       <c r="L8" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -35296,10 +35296,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>201.8214081244682</v>
       </c>
       <c r="K9" t="n">
-        <v>238</v>
+        <v>26.16709490985328</v>
       </c>
       <c r="L9" t="n">
         <v>62.07170870020967</v>
@@ -35308,13 +35308,13 @@
         <v>238</v>
       </c>
       <c r="N9" t="n">
-        <v>114.6018216761256</v>
+        <v>238</v>
       </c>
       <c r="O9" t="n">
-        <v>51.71030800750304</v>
+        <v>126.9609188808639</v>
       </c>
       <c r="P9" t="n">
-        <v>238</v>
+        <v>49.3627077684434</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35451,7 +35451,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>15.24198529897893</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>93.58977264938204</v>
@@ -35460,7 +35460,7 @@
         <v>192.7871909547739</v>
       </c>
       <c r="L11" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35478,7 +35478,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>40.79295373129298</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>204.3566661966798</v>
@@ -35542,16 +35542,16 @@
         <v>62.07170870020967</v>
       </c>
       <c r="M12" t="n">
-        <v>50.72022173439683</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
+        <v>90.12107010711591</v>
+      </c>
+      <c r="O12" t="n">
+        <v>178.5103626775776</v>
+      </c>
+      <c r="P12" t="n">
         <v>238</v>
-      </c>
-      <c r="O12" t="n">
-        <v>127.7555495505602</v>
-      </c>
-      <c r="P12" t="n">
-        <v>49.3627077684434</v>
       </c>
       <c r="Q12" t="n">
         <v>143.1569357924021</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>108.831757948361</v>
+        <v>93.58977264938204</v>
       </c>
       <c r="K14" t="n">
         <v>192.7871909547739</v>
       </c>
       <c r="L14" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -35715,7 +35715,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>23.06537183876391</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>204.3566661966798</v>
       </c>
       <c r="K15" t="n">
+        <v>26.16709490985328</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62.07170870020967</v>
+      </c>
+      <c r="M15" t="n">
         <v>238</v>
       </c>
-      <c r="L15" t="n">
-        <v>125.3355833293967</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
-        <v>90.12107010711591</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>51.71030800750304</v>
       </c>
       <c r="P15" t="n">
-        <v>49.3627077684434</v>
+        <v>216.9211247771905</v>
       </c>
       <c r="Q15" t="n">
-        <v>160.4321311359355</v>
+        <v>143.1569357924021</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>93.58977264938204</v>
       </c>
       <c r="K17" t="n">
-        <v>208.0291762537528</v>
+        <v>192.7871909547739</v>
       </c>
       <c r="L17" t="n">
-        <v>238</v>
+        <v>238.0000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -35952,7 +35952,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -36016,19 +36016,19 @@
         <v>62.07170870020967</v>
       </c>
       <c r="M18" t="n">
-        <v>75.69821394960161</v>
+        <v>179.9377139710865</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>90.12107010711591</v>
       </c>
       <c r="O18" t="n">
-        <v>152.5926516527946</v>
+        <v>164.1445690992837</v>
       </c>
       <c r="P18" t="n">
-        <v>238</v>
+        <v>49.3627077684434</v>
       </c>
       <c r="Q18" t="n">
-        <v>160.4321311359355</v>
+        <v>143.1569357924021</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36174,13 +36174,13 @@
         <v>238.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>200.3519398454894</v>
+        <v>185.1099545465106</v>
       </c>
       <c r="P20" t="n">
         <v>217.654934934193</v>
@@ -36241,28 +36241,28 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>23.06537183876391</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>204.3566661966798</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>26.16709490985328</v>
+        <v>211.7924861227831</v>
       </c>
       <c r="L21" t="n">
-        <v>205.2072399042394</v>
+        <v>62.07170870020967</v>
       </c>
       <c r="M21" t="n">
-        <v>50.72022173439683</v>
+        <v>238</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>51.71030800750304</v>
+        <v>238</v>
       </c>
       <c r="P21" t="n">
-        <v>238</v>
+        <v>49.3627077684434</v>
       </c>
       <c r="Q21" t="n">
         <v>143.1569357924021</v>
@@ -36423,10 +36423,10 @@
         <v>217.654934934193</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>15.24198529897893</v>
       </c>
       <c r="R23" t="n">
-        <v>15.24198529897881</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36481,25 +36481,25 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>204.3566661966798</v>
       </c>
       <c r="K24" t="n">
         <v>26.16709490985328</v>
       </c>
       <c r="L24" t="n">
+        <v>62.07170870020967</v>
+      </c>
+      <c r="M24" t="n">
         <v>238</v>
       </c>
-      <c r="M24" t="n">
-        <v>157.5760298060236</v>
-      </c>
       <c r="N24" t="n">
-        <v>90.12107010711591</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>238</v>
+        <v>51.71030800750304</v>
       </c>
       <c r="P24" t="n">
-        <v>49.3627077684434</v>
+        <v>216.9211247771905</v>
       </c>
       <c r="Q24" t="n">
         <v>143.1569357924021</v>
@@ -36654,10 +36654,10 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="P26" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36715,16 +36715,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>24.79295373129298</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>71.04884705607563</v>
       </c>
       <c r="K27" t="n">
-        <v>184</v>
+        <v>26.16709490985328</v>
       </c>
       <c r="L27" t="n">
-        <v>103.7951816765056</v>
+        <v>62.07170870020967</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -36733,10 +36733,10 @@
         <v>74.12107010711591</v>
       </c>
       <c r="O27" t="n">
-        <v>51.71030800750304</v>
+        <v>184</v>
       </c>
       <c r="P27" t="n">
-        <v>162.9892072508369</v>
+        <v>184</v>
       </c>
       <c r="Q27" t="n">
         <v>127.1569357924021</v>
@@ -36891,10 +36891,10 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="P29" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36952,19 +36952,19 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.065371838763905</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>111.2173990855476</v>
+        <v>123.5642818841477</v>
       </c>
       <c r="K30" t="n">
         <v>26.16709490985328</v>
       </c>
       <c r="L30" t="n">
-        <v>184</v>
+        <v>62.07170870020967</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>82.12185740348448</v>
       </c>
       <c r="N30" t="n">
         <v>74.12107010711591</v>
@@ -36973,10 +36973,10 @@
         <v>184</v>
       </c>
       <c r="P30" t="n">
-        <v>141.9947206243758</v>
+        <v>49.3627077684434</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>127.1569357924021</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37131,7 +37131,7 @@
         <v>184</v>
       </c>
       <c r="P32" t="n">
-        <v>184.0000000000001</v>
+        <v>184</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37189,28 +37189,28 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>8.065371838763905</v>
+        <v>25.79295373129298</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K33" t="n">
-        <v>26.16709490985328</v>
+        <v>184</v>
       </c>
       <c r="L33" t="n">
-        <v>184</v>
+        <v>62.07170870020967</v>
       </c>
       <c r="M33" t="n">
-        <v>35.72022173439683</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>75.12107010711591</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>70.05976683959204</v>
+        <v>77.90615522977501</v>
       </c>
       <c r="P33" t="n">
-        <v>184</v>
+        <v>49.3627077684434</v>
       </c>
       <c r="Q33" t="n">
         <v>145.4321311359355</v>
@@ -37429,7 +37429,7 @@
         <v>25.79295373129298</v>
       </c>
       <c r="J36" t="n">
-        <v>152.3499724586894</v>
+        <v>184</v>
       </c>
       <c r="K36" t="n">
         <v>184</v>
@@ -37441,16 +37441,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>75.12107010711591</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>51.71030800750304</v>
+        <v>77.90615522977501</v>
       </c>
       <c r="P36" t="n">
         <v>49.3627077684434</v>
       </c>
       <c r="Q36" t="n">
-        <v>128.1569357924021</v>
+        <v>145.4321311359355</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37663,16 +37663,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>25.79295373129297</v>
+        <v>25.79295373129298</v>
       </c>
       <c r="J39" t="n">
-        <v>160.6179902128059</v>
+        <v>184</v>
       </c>
       <c r="K39" t="n">
         <v>26.16709490985328</v>
       </c>
       <c r="L39" t="n">
-        <v>62.07170870020967</v>
+        <v>170.9793909055125</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -37681,7 +37681,7 @@
         <v>75.12107010711591</v>
       </c>
       <c r="O39" t="n">
-        <v>184</v>
+        <v>51.71030800750304</v>
       </c>
       <c r="P39" t="n">
         <v>49.3627077684434</v>
@@ -37742,7 +37742,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>58.81106897004568</v>
+        <v>58.81106897004567</v>
       </c>
       <c r="J40" t="n">
         <v>184</v>
@@ -37903,25 +37903,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
+        <v>46.71233833268708</v>
+      </c>
+      <c r="K42" t="n">
+        <v>27.16709490985328</v>
+      </c>
+      <c r="L42" t="n">
         <v>184</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>184</v>
       </c>
-      <c r="L42" t="n">
-        <v>63.07170870020967</v>
-      </c>
-      <c r="M42" t="n">
-        <v>60.78363985794392</v>
-      </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="O42" t="n">
         <v>52.71030800750304</v>
       </c>
       <c r="P42" t="n">
-        <v>184</v>
+        <v>49.97591531561321</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>167.7632711419113</v>
       </c>
       <c r="K45" t="n">
-        <v>184</v>
+        <v>27.16709490985328</v>
       </c>
       <c r="L45" t="n">
-        <v>62.56227473794551</v>
+        <v>63.07170870020967</v>
       </c>
       <c r="M45" t="n">
         <v>184</v>
@@ -38155,10 +38155,10 @@
         <v>184</v>
       </c>
       <c r="O45" t="n">
-        <v>63.6406740592676</v>
+        <v>52.71030800750304</v>
       </c>
       <c r="P45" t="n">
-        <v>50.3627077684434</v>
+        <v>49.85327380617925</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
